--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,54 +425,3324 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nombre_Buscado_Noticia</t>
+          <t>NROID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Contraparte_Encontrada</t>
+          <t>NIVEL DE ALERTA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CONTRAPARTE (BD)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ACUSADO (NOTICIA)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>% DE COINCIDENCIA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>DELITO</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>URL_NOTICIA</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CRISTIAN CAMILO CARO GUZMAN</t>
+          <t>13469446</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CAMILO  GUZMAN</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>JAIME  PENA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JESUS EDUARDO GUERRERO</t>
+          <t>1014200645</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JESUS EDUARDO GUERRERO RAMOS</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SEBASTIAN  JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JOSE RAFAEL ALTUVE HERNANDEZ</t>
+          <t>3021429</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JOSE RAFAEL HERNANDEZ</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>JAIME  MARTINEZ MORALES</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>79462042</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>JAIME  CARRILLO MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>14248964</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>JAIME  MARTINEZ DUARTE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1014206263</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES OLARTE MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>94071638</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>JAIME HERNANDO AYALA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1193426483</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>JAIME RICARDO MARTINEZ CORTES</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1075220472</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES MARTINEZ ARIAS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1143868024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>JAIME ALBERTO MUNOZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1047463434</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>JAIME RAMON VEGA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>88249713</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>JAIME OLARSEN CONTRERAS MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1019144662</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>JAIME ALEJANDRO CASTELLANOS MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>79695650</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>JAIME HERNANDO JARAMILLO MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>80174386</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>JAIME ALEJANDRO DIAZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1061739312</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>JHON JAIME MARTINEZ ALEGRIA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1002298732</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>JAIME ANTONIO MARTINEZ ROHENES</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1047480775</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>JAIME MANUEL MARTINEZ POLANCO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>16375864</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>JAIME ALBERTO MARTINEZ ROSERO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>73195967</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>JAIME LUIS PIZARRO MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>71667583</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CARLOS JAIME MARTINEZ GOMEZ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1026290959</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES TALERO MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>10294997</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>JAIME ALBERTO MARTINEZ VELASCO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1003232174</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>JOSE JAIME SILVA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>10771823</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>JAIME ALFONSO MARTINEZ MONTIEL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>80822124</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>JAIME ALEJANDRO PEDROZA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>80720324</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>JAIME BERNARDO MARTINEZ GAITAN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1193470087</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>JAIME MANUEL FIGUEROA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1001969453</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES GARCIA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1000254172</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES MARTINEZ HERRERA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1128419590</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES MARTINEZ LOAIZA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>98763511</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>JAIME STIVEN MARTINEZ CORREA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1014255448</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>JAIME ARMANDO MARTINEZ NAVARRETE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1053349090</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES MARTINEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>98393993</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>JAIME TOMAS MARTINEZ CANTUCA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1026305271</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>LUIS HARLEY JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1110551464</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>JAIME ESTEBAN BLANCO MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1152704412</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>JHON JAIME VERGARA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1005967725</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES ROSALES MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1067816876</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>JAVIER JAIME NORIEGA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>13959788</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES MARTINEZ ROMERO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1030686952</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES SILVA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1076242553</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES AYALA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1088313984</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES CABREJO MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1193148280</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES MARTINEZ CUELLAR</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>5823563</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>JAIME HERIBERTO MARTINEZ CORTES</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1113621540</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>JAIME EDUARDO ALVAREZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1065575270</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>JAIME ENRIQUE CARDENAS MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1033258099</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES MARTINEZ TORO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1143231049</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES MARTINEZ NOGUERA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1064803557</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>JAIME LUIS MARTINEZ MUNOZ</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>92509692</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>JAIME ALBERTO MARTINEZ FRANCO</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1193584574</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>JAIME FELIPE GOMEZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>80732159</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>IVAN DARIO TIBANA RIOS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1192793802</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>IVAN ARGEMIRO RIOS RIOS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>75097168</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>JORGE IVAN GONZALEZ RIOS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>71113528</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>JORGE IVAN RIOS MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1032439716</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DANIEL IVAN ALFONSO RIOS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1090423266</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>IVAN DARIO PRIETO RIOS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1193536763</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>JEISSON IVAN VASQUEZ RIOS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1112781755</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>IVAN ARTURO RIOS MONTOYA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1067966030</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>IVAN DAVID CORONADO RIOS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1007452033</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>IVAN ANDRES CHALJUB RIOS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1091202156</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>IVAN FERNANDO PINEDA RIOS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1098627381</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>IVAN ELIECER TARAZONA RIOS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1050778790</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>IVAN ANDRES RIOS FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1051064886</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>IVAN DARIO RIOS MANCIPE</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1007632193</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>JORGE IVAN RAMIREZ RIOS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1058818877</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SERGIO IVAN RIOS LOPEZ</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1000834735</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>IVAN ALFONSO TORRES RIOS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1010235985</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>IVAN FELIPE RIOS BONILLA</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1005230832</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>IVAN RICARDO RIOS GRANADOS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1043640839</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>IVAN ENRIQUE ARGEL RIOS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>93237498</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>HECTOR IVAN RIOS BERNATE</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1088260604</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>JORGE IVAN GOMEZ RIOS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1015415428</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>IVAN ARTURO RIOS VASQUEZ</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1047419894</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>JAIME DE JESUS VASQUEZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>JAIME MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ORDENAR MULTIPLES ACCIONES DELICTIVAS EN ZONA RURAL DE JAMUNDI (VALLE DEL CAUCA), CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE SECUESTRO, DESAPARICION FORZADA, AMENAZAS A CIVILES Y EXCOMBATIENTES, TERRORISMO, DESPLAZAMIENTO FORZADO, HOMICIDIO, HOMICIDIO AGRAVADO Y HOMICIDIO AGRAVADO EN GRADO DE TENTATIVA; ASI COMO FABRICACION, TRAFICO Y PORTE DE ARMAS, MUNICIONES DE USO RESTRINGIDO, DE USO PRIVATIVO DE LAS FUERZAS ARMADAS O EXPLOSIVOS Y SECUESTRO SIMPLE AGRAVADO</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-excomandante-de-la-columna-movil-jaime-martinez-senalado-de-multiples-delitos-en-zona-rural-de-jamundi-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1020763408</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>IVAN CAMILO DE LOS RIOS TOVAR</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>IVAN RIOS</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR AGRAVADO CON FINES DE HOMICIDIO, EXTORSION, DESPLAZAMIENTO FORZADO Y FINANCIACION DEL TERRORISMO; RECLUTAMIENTO ILICITO Y FABRICACION, TRAFICO Y PORTE DE ARMAS DE USO RESTRINGIDO</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/al-descubierto-uno-de-los-senalados-reclutadores-de-menores-de-edad-para-las-estructuras-armadas-de-las-disidencias-de-las-farc-en-el-oriente-del-pais/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,90 +467,6 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>URL_NOTICIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1067962652</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>JOSE FRANCISCO CHAVEZ SUAREZ</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>JOSE FRANCISCO SUAREZ</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>FEMINICIDIO AGRAVADO</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/sentido-de-fallo-condenatorio-contra-senalado-responsable-de-crimen-de-su-pareja-en-el-sur-de-bogota/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1110459415</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>JOSE FRANCISCO SUAREZ CAMACHO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>JOSE FRANCISCO SUAREZ</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>FEMINICIDIO AGRAVADO</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/sentido-de-fallo-condenatorio-contra-senalado-responsable-de-crimen-de-su-pareja-en-el-sur-de-bogota/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,48 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>URL_NOTICIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>94463387</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>JHON ALEXANDER MORENO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>JHON ALEXANDER MORENO CORDOBA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-presuntos-integrantes-de-los-los-mexicanos-que-estarian-implicados-en-89-hurtos-en-la-modalidad-de-fleteo/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>94463387</t>
+          <t>1001331059</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JHON ALEXANDER MORENO</t>
+          <t>ALEXANDER  VARGAS VARGAS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>JHON ALEXANDER MORENO CORDOBA</t>
+          <t>WILLIAM ALEXANDER MARRERO VARGAS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,17 +498,101 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
+          <t>PORTE DE ARMAS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-presuntos-integrantes-de-los-los-mexicanos-que-estarian-implicados-en-89-hurtos-en-la-modalidad-de-fleteo/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/en-cali-condenan-a-cuatro-personas-por-delitos-contra-la-vida/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1020470413</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ALEJANDRO  MUNOZ MUNOZ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>JHON ALEJANDRO MUNOZ SERNA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/en-bolivar-judicializan-a-siete-hombres-por-presunto-porte-ilegal-de-armas/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>19280244</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>JAIRO  FLOREZ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>JHON JAIRO FLOREZ DIOSA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/en-cali-condenan-a-cuatro-personas-por-delitos-contra-la-vida/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1001331059</t>
+          <t>1007633015</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ALEXANDER  VARGAS VARGAS</t>
+          <t>DAVID  ORTIZ ORTIZ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WILLIAM ALEXANDER MARRERO VARGAS</t>
+          <t>YEISON DAVID ANDRADE ORTIZ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,24 +498,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>PORTE DE ARMAS</t>
+          <t>EXTORSION</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/en-cali-condenan-a-cuatro-personas-por-delitos-contra-la-vida/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-participar-en-extorsiones-a-un-empresario-de-carga-en-narino/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1020470413</t>
+          <t>6825548</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ALEJANDRO  MUNOZ MUNOZ</t>
+          <t>EDUARDO JESUS LARA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JHON ALEJANDRO MUNOZ SERNA</t>
+          <t>JESUS EDUARDO YEPEZ LARA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,49 +550,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/en-bolivar-judicializan-a-siete-hombres-por-presunto-porte-ilegal-de-armas/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>19280244</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>JAIRO  FLOREZ</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>JHON JAIRO FLOREZ DIOSA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>PORTE DE ARMAS</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/en-cali-condenan-a-cuatro-personas-por-delitos-contra-la-vida/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/en-valledupar-aseguran-a-seis-personas-que-habrian-intentado-hurtar-un-vehiculo-de-valores/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,49 +473,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1007633015</t>
+          <t>1121944189</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DAVID  ORTIZ ORTIZ</t>
+          <t>LUIS FERNANDO CORTES MARTINEZ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>YEISON DAVID ANDRADE ORTIZ</t>
+          <t>LUIS FERNANDO CORTES MARTINEZ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EXTORSION</t>
+          <t>PORTE DE ARMAS, ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-participar-en-extorsiones-a-un-empresario-de-carga-en-narino/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/aseguradas-12-personas-que-estarian-involucradas-en-al-menos-10-homicidios-en-andalucia-valle-del-cauca/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6825548</t>
+          <t>1089600975</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EDUARDO JESUS LARA</t>
+          <t>ALEJANDRO  SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JESUS EDUARDO YEPEZ LARA</t>
+          <t>WILLI ALEJANDRO VELEZ SANCHEZ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -540,17 +540,269 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>PORTE DE ARMAS</t>
+          <t>ESTUPEFACIENTES, DROGA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/en-valledupar-aseguran-a-seis-personas-que-habrian-intentado-hurtar-un-vehiculo-de-valores/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/en-belen-de-umbria-fueron-judicializadas-cuatro-personas-por-presunto-trafico-local-de-estupefacientes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9102959</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ALEJANDRO  VELEZ VELEZ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>WILLI ALEJANDRO VELEZ SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, DROGA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/en-belen-de-umbria-fueron-judicializadas-cuatro-personas-por-presunto-trafico-local-de-estupefacientes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>71386620</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LUIS ALBERTO CANO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LUIS ALBERTO GALLEGO CANO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/aseguradas-12-personas-que-estarian-involucradas-en-al-menos-10-homicidios-en-andalucia-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>79987203</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ANDRES FELIPE CUELLAR</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ANDRES FELIPE GAMBOA CUELLAR</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/aseguradas-12-personas-que-estarian-involucradas-en-al-menos-10-homicidios-en-andalucia-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1018512286</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DAVID ALEJANDRO NINO VARGAS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ALEJANDRO VARGAS NINO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/aseguradas-12-personas-que-estarian-involucradas-en-al-menos-10-homicidios-en-andalucia-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1014273614</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DIEGO ALEJANDRO NINO VARGAS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ALEJANDRO VARGAS NINO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/aseguradas-12-personas-que-estarian-involucradas-en-al-menos-10-homicidios-en-andalucia-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>16749908</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FERNANDO  MARTINEZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO CORTES MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/aseguradas-12-personas-que-estarian-involucradas-en-al-menos-10-homicidios-en-andalucia-valle-del-cauca/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -599,7 +599,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>71386620</t>
+          <t>79987203</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO CANO</t>
+          <t>ANDRES FELIPE CUELLAR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO GALLEGO CANO</t>
+          <t>ANDRES FELIPE GAMBOA CUELLAR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -641,7 +641,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>79987203</t>
+          <t>1018512286</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ANDRES FELIPE CUELLAR</t>
+          <t>DAVID ALEJANDRO NINO VARGAS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ANDRES FELIPE GAMBOA CUELLAR</t>
+          <t>ALEJANDRO VARGAS NINO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1018512286</t>
+          <t>1014273614</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DAVID ALEJANDRO NINO VARGAS</t>
+          <t>DIEGO ALEJANDRO NINO VARGAS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1014273614</t>
+          <t>16749908</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DIEGO ALEJANDRO NINO VARGAS</t>
+          <t>FERNANDO  MARTINEZ MARTINEZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ALEJANDRO VARGAS NINO</t>
+          <t>LUIS FERNANDO CORTES MARTINEZ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -767,7 +767,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16749908</t>
+          <t>71386620</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -777,12 +777,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FERNANDO  MARTINEZ MARTINEZ</t>
+          <t>LUIS ALBERTO CANO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO CORTES MARTINEZ</t>
+          <t>LUIS ALBERTO GALLEGO CANO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -599,7 +599,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>79987203</t>
+          <t>71386620</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ANDRES FELIPE CUELLAR</t>
+          <t>LUIS ALBERTO CANO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ANDRES FELIPE GAMBOA CUELLAR</t>
+          <t>LUIS ALBERTO GALLEGO CANO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -641,7 +641,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1018512286</t>
+          <t>79987203</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DAVID ALEJANDRO NINO VARGAS</t>
+          <t>ANDRES FELIPE CUELLAR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ALEJANDRO VARGAS NINO</t>
+          <t>ANDRES FELIPE GAMBOA CUELLAR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1014273614</t>
+          <t>16749908</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DIEGO ALEJANDRO NINO VARGAS</t>
+          <t>FERNANDO  MARTINEZ MARTINEZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ALEJANDRO VARGAS NINO</t>
+          <t>LUIS FERNANDO CORTES MARTINEZ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16749908</t>
+          <t>1018512286</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FERNANDO  MARTINEZ MARTINEZ</t>
+          <t>DAVID ALEJANDRO NINO VARGAS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO CORTES MARTINEZ</t>
+          <t>ALEJANDRO VARGAS NINO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -767,7 +767,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>71386620</t>
+          <t>1014273614</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -777,12 +777,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO CANO</t>
+          <t>DIEGO ALEJANDRO NINO VARGAS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO GALLEGO CANO</t>
+          <t>ALEJANDRO VARGAS NINO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -599,7 +599,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>71386620</t>
+          <t>1018512286</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO CANO</t>
+          <t>DAVID ALEJANDRO NINO VARGAS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO GALLEGO CANO</t>
+          <t>ALEJANDRO VARGAS NINO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -641,7 +641,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>79987203</t>
+          <t>1014273614</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ANDRES FELIPE CUELLAR</t>
+          <t>DIEGO ALEJANDRO NINO VARGAS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ANDRES FELIPE GAMBOA CUELLAR</t>
+          <t>ALEJANDRO VARGAS NINO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1018512286</t>
+          <t>79987203</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DAVID ALEJANDRO NINO VARGAS</t>
+          <t>ANDRES FELIPE CUELLAR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ALEJANDRO VARGAS NINO</t>
+          <t>ANDRES FELIPE GAMBOA CUELLAR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -767,7 +767,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1014273614</t>
+          <t>71386620</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -777,12 +777,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DIEGO ALEJANDRO NINO VARGAS</t>
+          <t>LUIS ALBERTO CANO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ALEJANDRO VARGAS NINO</t>
+          <t>LUIS ALBERTO GALLEGO CANO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1121944189</t>
+          <t>1040047607</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO CORTES MARTINEZ</t>
+          <t>CARLOS ANDRES GARCIA MORALES</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO CORTES MARTINEZ</t>
+          <t>CARLOS ANDRES GARCIA MORALES</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,108 +498,108 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>PORTE DE ARMAS, ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>SECUESTRO, CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/aseguradas-12-personas-que-estarian-involucradas-en-al-menos-10-homicidios-en-andalucia-valle-del-cauca/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/fiscalia-afecta-a-red-delictiva-senalada-de-contactar-ciudadanos-extranjeros-por-redes-sociales-y-citarlos-para-retenerlos-y-robarles-las-pertenencias-en-cartagena/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1089600975</t>
+          <t>1007778510</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ALEJANDRO  SANCHEZ SANCHEZ</t>
+          <t>CARLOS ANDRES MORALES GARCIA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>WILLI ALEJANDRO VELEZ SANCHEZ</t>
+          <t>CARLOS ANDRES GARCIA MORALES</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, DROGA</t>
+          <t>SECUESTRO, CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/en-belen-de-umbria-fueron-judicializadas-cuatro-personas-por-presunto-trafico-local-de-estupefacientes/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/fiscalia-afecta-a-red-delictiva-senalada-de-contactar-ciudadanos-extranjeros-por-redes-sociales-y-citarlos-para-retenerlos-y-robarles-las-pertenencias-en-cartagena/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9102959</t>
+          <t>1023364409</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ALEJANDRO  VELEZ VELEZ</t>
+          <t>CARLOS ANDRES MORALES GARCIA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>WILLI ALEJANDRO VELEZ SANCHEZ</t>
+          <t>CARLOS ANDRES GARCIA MORALES</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, DROGA</t>
+          <t>SECUESTRO, CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/en-belen-de-umbria-fueron-judicializadas-cuatro-personas-por-presunto-trafico-local-de-estupefacientes/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/fiscalia-afecta-a-red-delictiva-senalada-de-contactar-ciudadanos-extranjeros-por-redes-sociales-y-citarlos-para-retenerlos-y-robarles-las-pertenencias-en-cartagena/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1018512286</t>
+          <t>91490479</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DAVID ALEJANDRO NINO VARGAS</t>
+          <t>JAVIER  FLOREZ ALVAREZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ALEJANDRO VARGAS NINO</t>
+          <t>PEDRO JAVIER FLOREZ ALVAREZ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -624,24 +624,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>PORTE DE ARMAS, ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>PORTE DE ARMAS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/aseguradas-12-personas-que-estarian-involucradas-en-al-menos-10-homicidios-en-andalucia-valle-del-cauca/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-el-conductor-de-un-vehiculo-en-el-que-habrian-sido-movilizados-hombres-implicados-en-un-ataque-armado-que-dejo-dos-muertos-y-un-herido/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1014273614</t>
+          <t>1053771833</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DIEGO ALEJANDRO NINO VARGAS</t>
+          <t>ANDRES  MORALES GARCIA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ALEJANDRO VARGAS NINO</t>
+          <t>CARLOS ANDRES GARCIA MORALES</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -666,143 +666,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>PORTE DE ARMAS, ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>SECUESTRO, CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/aseguradas-12-personas-que-estarian-involucradas-en-al-menos-10-homicidios-en-andalucia-valle-del-cauca/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>16749908</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>FERNANDO  MARTINEZ MARTINEZ</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LUIS FERNANDO CORTES MARTINEZ</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>PORTE DE ARMAS, ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/aseguradas-12-personas-que-estarian-involucradas-en-al-menos-10-homicidios-en-andalucia-valle-del-cauca/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>79987203</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ANDRES FELIPE CUELLAR</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ANDRES FELIPE GAMBOA CUELLAR</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>PORTE DE ARMAS, ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/aseguradas-12-personas-que-estarian-involucradas-en-al-menos-10-homicidios-en-andalucia-valle-del-cauca/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>71386620</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LUIS ALBERTO CANO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LUIS ALBERTO GALLEGO CANO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>PORTE DE ARMAS, ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/aseguradas-12-personas-que-estarian-involucradas-en-al-menos-10-homicidios-en-andalucia-valle-del-cauca/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/fiscalia-afecta-a-red-delictiva-senalada-de-contactar-ciudadanos-extranjeros-por-redes-sociales-y-citarlos-para-retenerlos-y-robarles-las-pertenencias-en-cartagena/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,133 +473,133 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1040047607</t>
+          <t>1093770203</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES GARCIA MORALES</t>
+          <t>DAVID  MUNOZ MUNOZ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES GARCIA MORALES</t>
+          <t>CRISTIAN DAVID SOLANO MUNOZ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SECUESTRO, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/fiscalia-afecta-a-red-delictiva-senalada-de-contactar-ciudadanos-extranjeros-por-redes-sociales-y-citarlos-para-retenerlos-y-robarles-las-pertenencias-en-cartagena/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1007778510</t>
+          <t>1005332663</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES MORALES GARCIA</t>
+          <t>DIEGO ANDRES LOPEZ VIVEROS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES GARCIA MORALES</t>
+          <t>DIEGO ANDRES LOPEZ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SECUESTRO, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/fiscalia-afecta-a-red-delictiva-senalada-de-contactar-ciudadanos-extranjeros-por-redes-sociales-y-citarlos-para-retenerlos-y-robarles-las-pertenencias-en-cartagena/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1023364409</t>
+          <t>1018501329</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES MORALES GARCIA</t>
+          <t>DIEGO ANDRES PACHON LOPEZ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES GARCIA MORALES</t>
+          <t>DIEGO ANDRES LOPEZ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SECUESTRO, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/fiscalia-afecta-a-red-delictiva-senalada-de-contactar-ciudadanos-extranjeros-por-redes-sociales-y-citarlos-para-retenerlos-y-robarles-las-pertenencias-en-cartagena/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>91490479</t>
+          <t>1002162552</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JAVIER  FLOREZ ALVAREZ</t>
+          <t>DIEGO ANDRES PADILLA LOPEZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PEDRO JAVIER FLOREZ ALVAREZ</t>
+          <t>DIEGO ANDRES LOPEZ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -624,24 +624,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>PORTE DE ARMAS</t>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-el-conductor-de-un-vehiculo-en-el-que-habrian-sido-movilizados-hombres-implicados-en-un-ataque-armado-que-dejo-dos-muertos-y-un-herido/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1053771833</t>
+          <t>1082910934</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ANDRES  MORALES GARCIA</t>
+          <t>DIEGO ANDRES CONTRERAS LOPEZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES GARCIA MORALES</t>
+          <t>DIEGO ANDRES LOPEZ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -666,17 +666,1151 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SECUESTRO, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/fiscalia-afecta-a-red-delictiva-senalada-de-contactar-ciudadanos-extranjeros-por-redes-sociales-y-citarlos-para-retenerlos-y-robarles-las-pertenencias-en-cartagena/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1019004051</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ RICAURTE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1094973279</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES RIVEROS LOPEZ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1007723810</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ ORDONEZ</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>80756578</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ PENA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>80236738</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ CAMELO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1055837981</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1088352147</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES CARDONA LOPEZ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1098704490</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES SARMIENTO LOPEZ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1049634243</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES BAUTISTA LOPEZ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1095303262</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES SANDOVAL LOPEZ</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1193030818</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1045742662</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES NAVARRO LOPEZ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1124380676</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ ANAYA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1032407676</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES MEJIA LOPEZ</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1057605511</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES DIAZ LOPEZ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1233902933</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES MARTIN LOPEZ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>80771317</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES TRIANA LOPEZ</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1044215162</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES CAMARGO LOPEZ</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1069468885</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ SALGADO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7182239</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES BARRERA LOPEZ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1073714520</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ BENITEZ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>80028344</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ RANGEL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>DIEGO ANDRES LOPEZ</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1005323346</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DAVID  RODRIGUEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>JAMES DAVID BARRERO RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1015475972</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DAVID  RODRIGUEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>JAMES DAVID BARRERO RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1019132593</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DAVID  RODRIGUEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>JAMES DAVID BARRERO RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1015407566</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>RUBEN DARIO GARCIA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RUBEN DARIO HENAO GARCIA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-banda-delincuencial-dedicada-al-hurto-de-vehiculos-en-el-valle-de-aburra/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1032443577</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CAMILO  MEDINA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CRISTIAN CAMILO MEDINA REBELLON</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>FINANCIACION DEL TERRORISMO, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-integrante-de-las-disidencias-de-las-farc-senalado-de-reclutar-a-12-menores-de-edad-en-cauca-para-ponerlos-a-disposicion-de-estructuras-armadas-en-meta/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1093770203</t>
+          <t>1072249135</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DAVID  MUNOZ MUNOZ</t>
+          <t>ALEXANDER  PEREZ PEREZ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CRISTIAN DAVID SOLANO MUNOZ</t>
+          <t>JONNY ALEXANDER OCAMPO PEREZ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,24 +498,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/en-palmira-valle-del-cauca-fue-asegurado-un-hombre-senalado-de-conservar-narcoticos-que-luego-serian-comercializados/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1005332663</t>
+          <t>1003482047</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ VIVEROS</t>
+          <t>RAFAEL  RODRIGUEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>RAFAEL IGNACIO RODRIGUEZ ZAPATA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -540,1277 +540,1235 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/nueve-personas-senaladas-de-trafico-local-de-estupefacientes-en-leticia-amazonas-fueron-aseguradas/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1018501329</t>
+          <t>1088337130</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES PACHON LOPEZ</t>
+          <t>SANTIAGO  MESA MOSQUERA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.67%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1002162552</t>
+          <t>1037672485</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES PADILLA LOPEZ</t>
+          <t>JUANITA  MESA MOSQUERA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.67%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1082910934</t>
+          <t>1121302744</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES CONTRERAS LOPEZ</t>
+          <t>ALDAIR JOSE ZAPA BELLO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1019004051</t>
+          <t>1005708010</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ RICAURTE</t>
+          <t>ALDAIR JOSE MARTINEZ MURILLO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1094973279</t>
+          <t>1045715300</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES RIVEROS LOPEZ</t>
+          <t>ALDAIR JOSE PEREZ ROJANO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1007723810</t>
+          <t>1067892198</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ ORDONEZ</t>
+          <t>ALDAIR JOSE OROZCO JULIO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>80756578</t>
+          <t>1193577086</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ PENA</t>
+          <t>ALDAIR JOSE ULLOA MOSQUERA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>80236738</t>
+          <t>1082878850</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ CAMELO</t>
+          <t>ALDAIR JOSE BORJA GAMERO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1055837981</t>
+          <t>1104873716</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ SANCHEZ</t>
+          <t>ALDAIR JOSE MENDEZ SALGADO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1088352147</t>
+          <t>1194963169</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES CARDONA LOPEZ</t>
+          <t>ALDAIR JOSE LOPEZ CONSUEGRA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1098704490</t>
+          <t>1122416961</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES SARMIENTO LOPEZ</t>
+          <t>ALDAIR JOSE ACOSTA MENDOZA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1049634243</t>
+          <t>1143131279</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES BAUTISTA LOPEZ</t>
+          <t>ALDAIR JOSE CABALLERO TORRES</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1095303262</t>
+          <t>1001946738</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES SANDOVAL LOPEZ</t>
+          <t>JOSE ALDAIR MOLINA MENDEZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1193030818</t>
+          <t>1045751253</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ RODRIGUEZ</t>
+          <t>ALDAIR JOSE OLIVERA MEJIA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1045742662</t>
+          <t>1193580567</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES NAVARRO LOPEZ</t>
+          <t>ALDAIR JOSE GUILLEN LIZARAZO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1124380676</t>
+          <t>1149439193</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ ANAYA</t>
+          <t>ALDAIR JOSE ESCORCIA RUIZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1032407676</t>
+          <t>1221967868</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES MEJIA LOPEZ</t>
+          <t>ALDAIR JOSE FERNANDEZ CUETO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1057605511</t>
+          <t>1090431586</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES DIAZ LOPEZ</t>
+          <t>ALDAIR JOSE SEGURA COLMENARES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1233902933</t>
+          <t>1000611623</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES MARTIN LOPEZ</t>
+          <t>JOSE GABRIEL MESA MOSQUERA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>80771317</t>
+          <t>79876845</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES TRIANA LOPEZ</t>
+          <t>JUAN CARLOS MOSQUERA MESA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1044215162</t>
+          <t>1020769964</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES CAMARGO LOPEZ</t>
+          <t>JESUS ARNEY MESA MOSQUERA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1069468885</t>
+          <t>1020831658</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ SALGADO</t>
+          <t>MARIA PAULA MESA MOSQUERA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7182239</t>
+          <t>1127630573</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES BARRERA LOPEZ</t>
+          <t>OSCAR IVAN MESA MOSQUERA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1073714520</t>
+          <t>1110519813</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ BENITEZ</t>
+          <t>ANTONIO  OVIEDO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>JESUS ANTONIO PACHECO OVIEDO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>SECUESTRO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/comunicado-de-prensa-431/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>80028344</t>
+          <t>52864978</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ RANGEL</t>
+          <t>CAROLINA  MESA DE LA OSSA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DIEGO ANDRES LOPEZ</t>
+          <t>LA MESA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1005323346</t>
+          <t>1094962232</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DAVID  RODRIGUEZ RODRIGUEZ</t>
+          <t>LAURA  MOSQUERA LOPEZ DE MESA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JAMES DAVID BARRERO RODRIGUEZ</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1015475972</t>
+          <t>88191792</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DAVID  RODRIGUEZ RODRIGUEZ</t>
+          <t>JOSE DE LA CRUZ ESPINEL MESA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>JAMES DAVID BARRERO RODRIGUEZ</t>
+          <t>LA MESA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>33.33%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1019132593</t>
+          <t>51994310</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DAVID  RODRIGUEZ RODRIGUEZ</t>
+          <t>ALEXANDRA JULIETA MESA DE LA OSSA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>JAMES DAVID BARRERO RODRIGUEZ</t>
+          <t>LA MESA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>33.33%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-el-barrio-centro-de-ibague-tolima/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1015407566</t>
+          <t>72273620</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RUBEN DARIO GARCIA</t>
+          <t>CARLOS ALBERTO DE LA OSSA MESA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RUBEN DARIO HENAO GARCIA</t>
+          <t>LA MESA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>33.33%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-integrantes-de-banda-delincuencial-dedicada-al-hurto-de-vehiculos-en-el-valle-de-aburra/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>1032443577</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CAMILO  MEDINA</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>CRISTIAN CAMILO MEDINA REBELLON</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>FINANCIACION DEL TERRORISMO, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-integrante-de-las-disidencias-de-las-farc-senalado-de-reclutar-a-12-menores-de-edad-en-cauca-para-ponerlos-a-disposicion-de-estructuras-armadas-en-meta/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,35 +436,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>RAPPIPAY ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>NIVEL DE ALERTA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>CONTRAPARTE (BD)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ACUSADO (NOTICIA)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>% DE COINCIDENCIA</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>FECHA</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>DELITO</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>URL_NOTICIA</t>
         </is>
@@ -473,208 +483,258 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1072249135</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ALEXANDER  PEREZ PEREZ</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>JONNY ALEXANDER OCAMPO PEREZ</t>
+          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>KATHERINE ANDREA BARRANTES MARTINEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>KATHERINE ANDREA MARTINEZ MARTINEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/en-palmira-valle-del-cauca-fue-asegurado-un-hombre-senalado-de-conservar-narcoticos-que-luego-serian-comercializados/</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/seccionales/seccional-bogota/implicado-en-magnicidio-del-senador-y-precandidato-presidencial-miguel-uribe-turbay-sera-condenado-mediante-preacuerdo-a-21-anos-de-prision/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1003482047</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>NO DISPONIBLE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NO DISPONIBLE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>🟠 ALERTA MEDIA (3 Palabras)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>RAFAEL  RODRIGUEZ RODRIGUEZ</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>RAFAEL IGNACIO RODRIGUEZ ZAPATA</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>YHON MAURICIO HURTADO MORENO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MAURICIO HURTADO MORENO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>75.0%</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/nueve-personas-senaladas-de-trafico-local-de-estupefacientes-en-leticia-amazonas-fueron-aseguradas/</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1088337130</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SANTIAGO  MESA MOSQUERA</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MOSQUERA MESA</t>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66.67%</t>
+          <t>EDUARDO  GONZALEZ GONZALEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CARLOS EDUARDO MORA GONZALEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/seccionales/seccional-bogota/implicado-en-magnicidio-del-senador-y-precandidato-presidencial-miguel-uribe-turbay-sera-condenado-mediante-preacuerdo-a-21-anos-de-prision/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1037672485</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JUANITA  MESA MOSQUERA</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MOSQUERA MESA</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>66.67%</t>
+          <t>ALDAIR JOSE BORJA GAMERO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1121302744</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>NO DISPONIBLE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>ALDAIR JOSE ZAPA BELLO</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>ALDAIR JOSE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -683,40 +743,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1005708010</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE MARTINEZ MURILLO</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ALDAIR JOSE GUILLEN LIZARAZO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>ALDAIR JOSE</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -725,40 +795,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1045715300</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE PEREZ ROJANO</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ALDAIR JOSE SEGURA COLMENARES</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>ALDAIR JOSE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -767,40 +847,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1067892198</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE OROZCO JULIO</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ALDAIR JOSE ESCORCIA RUIZ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>ALDAIR JOSE</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -809,40 +899,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1193577086</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE ULLOA MOSQUERA</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ALDAIR JOSE OLIVERA MEJIA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>ALDAIR JOSE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -851,40 +951,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1082878850</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE BORJA GAMERO</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ALDAIR JOSE CABALLERO TORRES</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>ALDAIR JOSE</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -893,40 +1003,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1104873716</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE MENDEZ SALGADO</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ALDAIR JOSE MARTINEZ MURILLO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>ALDAIR JOSE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -935,40 +1055,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1194963169</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE LOPEZ CONSUEGRA</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ALDAIR JOSE MENDEZ SALGADO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>ALDAIR JOSE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -977,40 +1107,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1122416961</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE ACOSTA MENDOZA</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ALDAIR JOSE FERNANDEZ CUETO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>ALDAIR JOSE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1019,40 +1159,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1143131279</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE CABALLERO TORRES</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ALDAIR JOSE ACOSTA MENDOZA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>ALDAIR JOSE</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1061,40 +1211,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1001946738</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>NO DISPONIBLE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>JOSE ALDAIR MOLINA MENDEZ</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>ALDAIR JOSE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1103,40 +1263,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1045751253</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE OLIVERA MEJIA</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ALDAIR JOSE MARTINEZ MIER</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>ALDAIR JOSE</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1145,40 +1315,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1193580567</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE GUILLEN LIZARAZO</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ALDAIR JOSE NAVARRO BERMEJO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>ALDAIR JOSE</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1187,40 +1367,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1149439193</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE ESCORCIA RUIZ</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ALDAIR JOSE MEZA ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>ALDAIR JOSE</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1229,40 +1419,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1221967868</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE FERNANDEZ CUETO</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ALDAIR JOSE HUERTAS FLOREZ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>ALDAIR JOSE</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1271,82 +1471,102 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1090431586</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE SEGURA COLMENARES</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>JOSE GABRIEL MESA MOSQUERA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1000611623</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>JOSE GABRIEL MESA MOSQUERA</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>JESUS ARNEY MESA MOSQUERA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>MOSQUERA MESA</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>ESTUPEFACIENTES</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
@@ -1355,40 +1575,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>79876845</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JUAN CARLOS MOSQUERA MESA</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>OSCAR IVAN MESA MOSQUERA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>MOSQUERA MESA</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>ESTUPEFACIENTES</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
@@ -1397,40 +1627,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1020769964</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JESUS ARNEY MESA MOSQUERA</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MARIA PAULA MESA MOSQUERA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>MOSQUERA MESA</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>ESTUPEFACIENTES</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
@@ -1439,40 +1679,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1020831658</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MARIA PAULA MESA MOSQUERA</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS MOSQUERA MESA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>MOSQUERA MESA</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>ESTUPEFACIENTES</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
@@ -1481,292 +1731,102 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1127630573</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>OSCAR IVAN MESA MOSQUERA</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MOSQUERA MESA</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>ANTONIO  OVIEDO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>JESUS ANTONIO PACHECO OVIEDO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>SECUESTRO</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/comunicado-de-prensa-431/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1110519813</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ANTONIO  OVIEDO</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>JESUS ANTONIO PACHECO OVIEDO</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>LAURA  MOSQUERA LOPEZ DE MESA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SECUESTRO</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/comunicado-de-prensa-431/</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>52864978</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CAROLINA  MESA DE LA OSSA</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>LA MESA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>ESTUPEFACIENTES</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1094962232</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>LAURA  MOSQUERA LOPEZ DE MESA</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>MOSQUERA MESA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>88191792</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>JOSE DE LA CRUZ ESPINEL MESA</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>LA MESA</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>33.33%</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>51994310</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>ALEXANDRA JULIETA MESA DE LA OSSA</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>LA MESA</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>33.33%</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>72273620</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CARLOS ALBERTO DE LA OSSA MESA</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>LA MESA</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>33.33%</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,56 +425,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NROID</t>
+          <t>DOCUMENTO</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PAY_ID</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>RAPPIPAY ID</t>
+          <t>NIVEL DE ALERTA</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>NIVEL DE ALERTA</t>
+          <t>CONTRAPARTE (BD)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>CONTRAPARTE (BD)</t>
+          <t>ACUSADO (NOTICIA)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ACUSADO (NOTICIA)</t>
+          <t>% DE COINCIDENCIA</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>% DE COINCIDENCIA</t>
+          <t>FECHA</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>FECHA</t>
+          <t>DELITO</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>DELITO</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>URL_NOTICIA</t>
         </is>
@@ -483,50 +478,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1022392209</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>93d006c6-fbfe-49bc-b400-ee2b79fe2c1c</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
+          <t>KATHERINE ANDREA BARRANTES MARTINEZ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KATHERINE ANDREA BARRANTES MARTINEZ</t>
+          <t>KATHERINE ANDREA MARTINEZ MARTINEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>KATHERINE ANDREA MARTINEZ MARTINEZ</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/seccionales/seccional-bogota/implicado-en-magnicidio-del-senador-y-precandidato-presidencial-miguel-uribe-turbay-sera-condenado-mediante-preacuerdo-a-21-anos-de-prision/</t>
         </is>
@@ -535,50 +525,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1017133362</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>82f1d569-6188-4279-af8d-45b1ea16cbdb</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>YHON MAURICIO HURTADO MORENO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>YHON MAURICIO HURTADO MORENO</t>
+          <t>MAURICIO HURTADO MORENO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MAURICIO HURTADO MORENO</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -587,50 +572,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>79388403</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>4dc06bf9-9c9f-4ae2-9543-7c2c2ecb469d</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>EDUARDO  GONZALEZ GONZALEZ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>EDUARDO  GONZALEZ GONZALEZ</t>
+          <t>CARLOS EDUARDO MORA GONZALEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO MORA GONZALEZ</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/seccionales/seccional-bogota/implicado-en-magnicidio-del-senador-y-precandidato-presidencial-miguel-uribe-turbay-sera-condenado-mediante-preacuerdo-a-21-anos-de-prision/</t>
         </is>
@@ -639,50 +619,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1082878850</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>3bcda606-c8d4-43c9-8de5-60e667f3a662</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>ALDAIR JOSE BORJA GAMERO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE BORJA GAMERO</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -691,50 +666,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1121302744</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>d832f365-2088-4d68-a94d-35cb0a7f5dcd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>ALDAIR JOSE ZAPA BELLO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE ZAPA BELLO</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -743,50 +713,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1193580567</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>f15c9081-8209-45f7-8dfd-40d244603d5e</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>ALDAIR JOSE GUILLEN LIZARAZO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE GUILLEN LIZARAZO</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -795,50 +760,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1090431586</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1acc496d-3410-442b-8a5f-d0c21595122a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>ALDAIR JOSE SEGURA COLMENARES</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE SEGURA COLMENARES</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -847,50 +807,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1149439193</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>bffc9b00-9eeb-40b9-ad59-09dcf77625ed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>ALDAIR JOSE ESCORCIA RUIZ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE ESCORCIA RUIZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -899,50 +854,45 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1045751253</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>d13b2209-4449-437c-903d-d9c178b61c0d</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>ALDAIR JOSE OLIVERA MEJIA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE OLIVERA MEJIA</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -951,50 +901,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1143131279</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>bb58ffe4-eecb-44c9-b85b-2d7eb5c15699</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>ALDAIR JOSE CABALLERO TORRES</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE CABALLERO TORRES</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1003,50 +948,45 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1005708010</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>38194de4-dd20-4121-8031-0643c0b6dc63</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>ALDAIR JOSE MARTINEZ MURILLO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE MARTINEZ MURILLO</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1055,50 +995,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1104873716</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>4c2750d0-ab8e-4799-89cb-8b5ff27d0313</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>ALDAIR JOSE MENDEZ SALGADO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE MENDEZ SALGADO</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1107,50 +1042,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1221967868</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>2ef8bbab-8460-4606-9e13-9f9298691c67</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>ALDAIR JOSE FERNANDEZ CUETO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE FERNANDEZ CUETO</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1159,50 +1089,45 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1122416961</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>ddd0f2d4-e211-4bff-95e9-a93df1b1cc6f</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>ALDAIR JOSE ACOSTA MENDOZA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE ACOSTA MENDOZA</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1211,50 +1136,45 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1001946738</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>44647ed3-3dc9-4c16-95fc-b78b96716a6d</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>JOSE ALDAIR MOLINA MENDEZ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JOSE ALDAIR MOLINA MENDEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1263,50 +1183,45 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1003314554</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>689e354a-1131-4d45-929b-8af052cffba5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>ALDAIR JOSE MARTINEZ MIER</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE MARTINEZ MIER</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1315,50 +1230,45 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1043018386</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>cb523411-be3c-4aa9-ab0a-dc135e9f318f</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>ALDAIR JOSE NAVARRO BERMEJO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE NAVARRO BERMEJO</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1367,50 +1277,45 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1001824421</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>2683b4dc-a86f-4f1c-9ba5-87fe0c33c931</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>ALDAIR JOSE MEZA ALVAREZ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE MEZA ALVAREZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1419,50 +1324,45 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1020793335</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>bec80240-7253-47af-9e2a-98ba39d17fdf</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>ALDAIR JOSE HUERTAS FLOREZ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE HUERTAS FLOREZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
@@ -1471,50 +1371,45 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1000611623</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>f2ba882f-89b4-4fd5-8af0-46fb57b76b90</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>JOSE GABRIEL MESA MOSQUERA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>JOSE GABRIEL MESA MOSQUERA</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MOSQUERA MESA</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
@@ -1523,50 +1418,45 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1020769964</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>e46ebe95-4f69-4b73-ab4d-b3bbcfddd0a5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>JESUS ARNEY MESA MOSQUERA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>JESUS ARNEY MESA MOSQUERA</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MOSQUERA MESA</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
@@ -1575,50 +1465,45 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1127630573</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>da72bf23-b357-4e7c-ace1-dca71c213a29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>OSCAR IVAN MESA MOSQUERA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OSCAR IVAN MESA MOSQUERA</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MOSQUERA MESA</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
@@ -1627,50 +1512,45 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1020831658</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>eff5ccac-b288-4934-a23e-bcd69efb1892</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>MARIA PAULA MESA MOSQUERA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MARIA PAULA MESA MOSQUERA</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MOSQUERA MESA</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
@@ -1679,50 +1559,45 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>79876845</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>6ea5fd42-e577-422c-9080-aa03de5c526f</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>JUAN CARLOS MOSQUERA MESA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>JUAN CARLOS MOSQUERA MESA</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MOSQUERA MESA</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
@@ -1731,50 +1606,45 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1110519813</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>4672fe0a-cd25-4fbe-aa71-29d51c441541</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>ANTONIO  OVIEDO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ANTONIO  OVIEDO</t>
+          <t>JESUS ANTONIO PACHECO OVIEDO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JESUS ANTONIO PACHECO OVIEDO</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>SECUESTRO</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
-        <is>
-          <t>SECUESTRO</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/comunicado-de-prensa-431/</t>
         </is>
@@ -1783,50 +1653,45 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>1094962232</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>2dc4eee9-e752-425e-b6ff-801502e828a2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>LAURA  MOSQUERA LOPEZ DE MESA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LAURA  MOSQUERA LOPEZ DE MESA</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MOSQUERA MESA</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,32 +478,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1022392209</t>
+          <t>1017133362</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>93d006c6-fbfe-49bc-b400-ee2b79fe2c1c</t>
+          <t>82f1d569-6188-4279-af8d-45b1ea16cbdb</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KATHERINE ANDREA BARRANTES MARTINEZ</t>
+          <t>YHON MAURICIO HURTADO MORENO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KATHERINE ANDREA MARTINEZ MARTINEZ</t>
+          <t>MAURICIO HURTADO MORENO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,44 +513,44 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/seccionales/seccional-bogota/implicado-en-magnicidio-del-senador-y-precandidato-presidencial-miguel-uribe-turbay-sera-condenado-mediante-preacuerdo-a-21-anos-de-prision/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1017133362</t>
+          <t>1082878850</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82f1d569-6188-4279-af8d-45b1ea16cbdb</t>
+          <t>3bcda606-c8d4-43c9-8de5-60e667f3a662</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>YHON MAURICIO HURTADO MORENO</t>
+          <t>ALDAIR JOSE BORJA GAMERO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MAURICIO HURTADO MORENO</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -572,32 +572,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>79388403</t>
+          <t>1121302744</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4dc06bf9-9c9f-4ae2-9543-7c2c2ecb469d</t>
+          <t>d832f365-2088-4d68-a94d-35cb0a7f5dcd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EDUARDO  GONZALEZ GONZALEZ</t>
+          <t>ALDAIR JOSE ZAPA BELLO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO MORA GONZALEZ</t>
+          <t>ALDAIR JOSE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -607,24 +607,24 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/seccionales/seccional-bogota/implicado-en-magnicidio-del-senador-y-precandidato-presidencial-miguel-uribe-turbay-sera-condenado-mediante-preacuerdo-a-21-anos-de-prision/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1082878850</t>
+          <t>1193580567</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3bcda606-c8d4-43c9-8de5-60e667f3a662</t>
+          <t>f15c9081-8209-45f7-8dfd-40d244603d5e</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE BORJA GAMERO</t>
+          <t>ALDAIR JOSE GUILLEN LIZARAZO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -666,12 +666,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1121302744</t>
+          <t>1090431586</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>d832f365-2088-4d68-a94d-35cb0a7f5dcd</t>
+          <t>1acc496d-3410-442b-8a5f-d0c21595122a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE ZAPA BELLO</t>
+          <t>ALDAIR JOSE SEGURA COLMENARES</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1193580567</t>
+          <t>1149439193</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>f15c9081-8209-45f7-8dfd-40d244603d5e</t>
+          <t>bffc9b00-9eeb-40b9-ad59-09dcf77625ed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE GUILLEN LIZARAZO</t>
+          <t>ALDAIR JOSE ESCORCIA RUIZ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -760,12 +760,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1090431586</t>
+          <t>1045751253</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1acc496d-3410-442b-8a5f-d0c21595122a</t>
+          <t>d13b2209-4449-437c-903d-d9c178b61c0d</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE SEGURA COLMENARES</t>
+          <t>ALDAIR JOSE OLIVERA MEJIA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -807,12 +807,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1149439193</t>
+          <t>1143131279</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bffc9b00-9eeb-40b9-ad59-09dcf77625ed</t>
+          <t>bb58ffe4-eecb-44c9-b85b-2d7eb5c15699</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE ESCORCIA RUIZ</t>
+          <t>ALDAIR JOSE CABALLERO TORRES</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -854,12 +854,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1045751253</t>
+          <t>1005708010</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>d13b2209-4449-437c-903d-d9c178b61c0d</t>
+          <t>38194de4-dd20-4121-8031-0643c0b6dc63</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE OLIVERA MEJIA</t>
+          <t>ALDAIR JOSE MARTINEZ MURILLO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -901,12 +901,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1143131279</t>
+          <t>1104873716</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bb58ffe4-eecb-44c9-b85b-2d7eb5c15699</t>
+          <t>4c2750d0-ab8e-4799-89cb-8b5ff27d0313</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE CABALLERO TORRES</t>
+          <t>ALDAIR JOSE MENDEZ SALGADO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -948,12 +948,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1005708010</t>
+          <t>1221967868</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>38194de4-dd20-4121-8031-0643c0b6dc63</t>
+          <t>2ef8bbab-8460-4606-9e13-9f9298691c67</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE MARTINEZ MURILLO</t>
+          <t>ALDAIR JOSE FERNANDEZ CUETO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -995,12 +995,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1104873716</t>
+          <t>1122416961</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4c2750d0-ab8e-4799-89cb-8b5ff27d0313</t>
+          <t>ddd0f2d4-e211-4bff-95e9-a93df1b1cc6f</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE MENDEZ SALGADO</t>
+          <t>ALDAIR JOSE ACOSTA MENDOZA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1042,12 +1042,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1221967868</t>
+          <t>1003314554</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2ef8bbab-8460-4606-9e13-9f9298691c67</t>
+          <t>689e354a-1131-4d45-929b-8af052cffba5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE FERNANDEZ CUETO</t>
+          <t>ALDAIR JOSE MARTINEZ MIER</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1089,12 +1089,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1122416961</t>
+          <t>1043018386</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ddd0f2d4-e211-4bff-95e9-a93df1b1cc6f</t>
+          <t>cb523411-be3c-4aa9-ab0a-dc135e9f318f</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE ACOSTA MENDOZA</t>
+          <t>ALDAIR JOSE NAVARRO BERMEJO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1136,12 +1136,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1001946738</t>
+          <t>1001824421</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>44647ed3-3dc9-4c16-95fc-b78b96716a6d</t>
+          <t>2683b4dc-a86f-4f1c-9ba5-87fe0c33c931</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>JOSE ALDAIR MOLINA MENDEZ</t>
+          <t>ALDAIR JOSE MEZA ALVAREZ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1183,12 +1183,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1003314554</t>
+          <t>1020793335</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>689e354a-1131-4d45-929b-8af052cffba5</t>
+          <t>bec80240-7253-47af-9e2a-98ba39d17fdf</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE MARTINEZ MIER</t>
+          <t>ALDAIR JOSE HUERTAS FLOREZ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1230,12 +1230,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1043018386</t>
+          <t>79876845</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cb523411-be3c-4aa9-ab0a-dc135e9f318f</t>
+          <t>6ea5fd42-e577-422c-9080-aa03de5c526f</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE NAVARRO BERMEJO</t>
+          <t>JUAN CARLOS MOSQUERA MESA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1001824421</t>
+          <t>1110519813</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2683b4dc-a86f-4f1c-9ba5-87fe0c33c931</t>
+          <t>4672fe0a-cd25-4fbe-aa71-29d51c441541</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE MEZA ALVAREZ</t>
+          <t>ANTONIO  OVIEDO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>JESUS ANTONIO PACHECO OVIEDO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1312,24 +1312,24 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
+          <t>SECUESTRO</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/comunicado-de-prensa-431/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1020793335</t>
+          <t>1094962232</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>bec80240-7253-47af-9e2a-98ba39d17fdf</t>
+          <t>2dc4eee9-e752-425e-b6ff-801502e828a2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE HUERTAS FLOREZ</t>
+          <t>LAURA  MOSQUERA LOPEZ DE MESA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ALDAIR JOSE</t>
+          <t>MOSQUERA MESA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1359,339 +1359,10 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1000611623</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>f2ba882f-89b4-4fd5-8af0-46fb57b76b90</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>JOSE GABRIEL MESA MOSQUERA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>MOSQUERA MESA</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1020769964</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>e46ebe95-4f69-4b73-ab4d-b3bbcfddd0a5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>JESUS ARNEY MESA MOSQUERA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>MOSQUERA MESA</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>1127630573</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>da72bf23-b357-4e7c-ace1-dca71c213a29</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>OSCAR IVAN MESA MOSQUERA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>MOSQUERA MESA</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1020831658</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>eff5ccac-b288-4934-a23e-bcd69efb1892</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>MARIA PAULA MESA MOSQUERA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>MOSQUERA MESA</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>79876845</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>6ea5fd42-e577-422c-9080-aa03de5c526f</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>JUAN CARLOS MOSQUERA MESA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>MOSQUERA MESA</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>1110519813</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>4672fe0a-cd25-4fbe-aa71-29d51c441541</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ANTONIO  OVIEDO</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>JESUS ANTONIO PACHECO OVIEDO</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>SECUESTRO</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/comunicado-de-prensa-431/</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1094962232</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2dc4eee9-e752-425e-b6ff-801502e828a2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>LAURA  MOSQUERA LOPEZ DE MESA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>MOSQUERA MESA</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-responsable-de-transportar-mas-de-300-kilos-de-marihuana-en-mosquera-cundinamarca/</t>
         </is>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,100 +472,6 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>URL_NOTICIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1017133362</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>82f1d569-6188-4279-af8d-45b1ea16cbdb</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>YHON MAURICIO HURTADO MORENO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MAURICIO HURTADO MORENO</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/presuntos-integrantes-de-una-organizacion-delincuencial-dedicada-al-hurto-en-el-sur-de-medellin-fueron-enviados-a-la-carcel/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1110519813</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>4672fe0a-cd25-4fbe-aa71-29d51c441541</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ANTONIO  OVIEDO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>JESUS ANTONIO PACHECO OVIEDO</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SECUESTRO</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/comunicado-de-prensa-431/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,6 +475,3014 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1110508660</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>f91148d1-ec55-4752-a63d-f4f65d506b0f</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CARLOS  MOLANO PATINO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>79782900</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5cecd100-6ea6-4011-b8d6-75aa949a0cef</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CARLOS EDUARDO PATINO GOMEZ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1015995474</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>87096349-59aa-4e18-a4b3-3739e0b8f9d3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO CEBALLOS PATINO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1127246130</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>efdd7814-d9ec-4b7e-a577-80b9a39b893c</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CARLOS SAUL ORDONEZ PATINO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10186239</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8d5b5c44-4bf1-41bf-b64d-682ff1c66f9a</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>JOSE CARLOS PATINO TORRES</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1024597625</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1ccd17c1-b7c0-48ba-a5b1-f35dc84fe985</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CARLOS DANIEL PATINO ALVAREZ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>12753448</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>f5360ff2-d0aa-48b0-8023-818c5b49f4ba</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CARLOS EDUARDO GARCIA PATINO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1090450095</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1648e2b7-409f-434c-8257-1d56c09930c4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CARLOS EDUARDO PATINO PABON</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1044604037</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>442d112b-8e1f-4cc7-aa09-dacd39b3226b</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS MARTINEZ PATINO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>80773120</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>d238de83-6673-4098-9eb3-d082f1433d5f</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CARLOS HERNAN LOPEZ PATINO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1039469469</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>082cce38-b173-4cea-b792-34ef3d236930</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS RIOS PATINO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1144029836</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>8012b3e9-2e46-472a-8991-fddc1bf2847e</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES CABAL PATINO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1002567379</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>c98b569f-90c3-4f40-be02-3f4e8368a86f</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CARLOS MANUEL BOTERO PATINO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1020826607</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2ef0b0a0-c7e2-4174-be71-484f772fc156</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES PATINO LOPEZ</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>10030664</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>58efc384-cd5d-45ea-82e3-a6f096e6da99</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CARLOS ANIBAL PATINO RAMIREZ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>79945824</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>a4319a5a-7178-4826-a054-1fc82ba3b2a9</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CARLOS AUREL PATINO ECHEVERRI</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>80822149</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>c2781408-6e0f-4957-adef-cf5b45dbf7ba</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LUIS CARLOS TOBAR PATINO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>80255197</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>deab6738-62ca-4f49-9299-4766f98097ca</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS CARDENAS PATINO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1004624263</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>e4769e5f-b184-4d9e-a325-277bca59ba68</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO MOLINA PATINO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1042854584</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>28e60d16-7821-414c-81c0-08e9a0119af7</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CARLOS ALFONSO CALABRIA PATINO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>80011661</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>e9297d63-8a8a-4bad-a6eb-b6e0c95f5905</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CARLOS AUGUSTO NEIRA PATINO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1024571384</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>b96bb9c7-c3fb-490d-9a40-8c42237f0bf0</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS GALEANO PATINO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1010093562</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>dbf6f035-2e66-492e-a3f3-72c7e67f7077</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS GOMEZ PATINO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1090987718</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>8287037c-603c-4952-805c-1705e21b244b</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CARLOS MARIO PATINO RIOS</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>71291775</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>b2296f2e-0f8b-477b-935e-11d5eba248f5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CARLOS AUGUSTO RUIZ PATINO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>71384730</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>012dd7e3-0710-4ebd-982e-cef32ee80eb3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES BOTERO PATINO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>88252671</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>72b28ae6-85a3-4d13-a271-2fb8dc5a82a8</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CARLOS MANUEL PATINO MACHADO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1010245307</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3cb42c84-08b4-4a71-a7cc-7f75f7fccadf</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CARLOS EDUARDO GUEVARA PATINO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1042852549</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>b151199f-9222-49ec-8c73-831552ad6c0e</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CARLOS MIGUEL CALABRIA PATINO</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1148701468</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2d56837a-4ad2-4f10-888b-56b7643cdc27</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES PATINO HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1097402784</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>eb540e85-d60b-4b2a-b00d-0df6ceda8d6f</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CARLOS ARTURO OSPINA PATINO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1151955585</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>dc8585e3-9062-4ff9-a8ea-776457d74671</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CARLOS EDUARDO CRUZ PATINO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1045680502</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>715bd418-acda-4388-8e1d-1275573d19b0</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES PATINO CABRERA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1102887727</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>48c7c54f-628a-4c8b-909d-5564775aacd5</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CARLOS LEONARDO MONROY PATINO</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1095838786</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>839aa280-4e7e-4b8b-914f-9a066b0586b0</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CARLOS EDUARDO PATINO BECERRA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>94418174</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>035f053a-5176-4e7c-b119-31851513a868</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS RUIZ PATINO</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>19465846</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>85a42ffd-7730-4caf-af61-27b607744eff</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CARLOS EDUARDO PATINO VARGAS</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1057582624</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>35a3aa4a-313f-4e83-b743-136ce931c0a2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LUIS CARLOS PATINO LAGOS</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>8064063</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>dfafa730-2393-4afc-8302-0c7cab9c4f36</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO PATINO LOPEZ</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>16723021</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>a6efd779-ce6c-4e90-b17d-0d74663612b2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS PATINO RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>14473070</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>022c85fa-855b-4156-b7fd-74676137d193</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS MURILLO PATINO</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1021803274</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>b92c0ad2-07ca-472d-831f-7d230d58dda3</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>JEAN CARLOS MONTOYA PATINO</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1035833688</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>15ccf04c-4a93-4c65-9469-456dac73354c</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES MUNOZ PATINO</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1014185154</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1cba96cc-1ae8-471c-bfac-3d1419e0c4f3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES PATINO GIL</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1010094927</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>6b660e90-a6ef-43e9-9811-7ff7dc1d17cb</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CARLOS DANIEL ORTIZ PATINO</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>98659911</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0104cbf2-9469-4d99-9914-460fcf022ab3</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS PATINO MANRIQUE</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>14136606</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2e00cc48-3a00-4bce-927b-45a5682e4c3c</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO PATINO HERRERA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1020806800</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>bd433edd-5c13-41f9-96e7-7644a1c5a0db</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES BARRETO PATINO</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>10117792</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>3cdeb45d-1610-42db-9a54-7711c2b65da0</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS JARAMILLO PATINO</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1013687267</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>4cbdc802-05d1-4806-a935-3644f5ce8b8c</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CARLOS ARTURO PATINO MARIN</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1019102664</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>4efc391c-e2a4-4d1b-9763-0bf3bac8a803</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>CARLOS JULIO PATINO SUAREZ</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1057609620</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2674895b-803f-4d30-9f8a-1e6d32d02595</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CARLOS ALFREDO PATINO MORENO</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1080266516</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2969fcac-6e7a-4adb-86ae-e3dfd272e3d1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES JURADO PATINO</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>7730808</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2aacb798-d57e-42f7-bac6-1a7077720666</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS PATINO VERGEL</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1098817537</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>04d0ea15-3d7e-447d-b937-d0d0bfe4b9f4</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES PATINO ROMERO</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1016110073</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>712158aa-4bb7-4b80-9a3b-2937048b133a</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CARLOS DANIEL PATINO GOMEZ</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1094909424</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>cb523290-1fe8-454c-b312-45905a6e38de</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>JOSE CARLOS PATINO BAQUERO</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1000707828</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>febf0db0-b921-457b-a86f-88a16b135420</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>CARLOS FELIPE PATINO ALVAREZ</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1017156499</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>d62cb0dc-6a84-4cd2-be5d-7a043a82b496</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CARLOS MARIO ARBOLEDA PATINO</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1233190969</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>a6de2b59-c436-4249-9047-1c5fa8f01b6c</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES CUASTUMAL PATINO</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1020487686</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0c1f2a63-16fc-476f-8c4d-64bc7f0a3c77</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CARLOS MARIO PATINO BETANCUR</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1106768796</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>eaca9f45-f36c-428c-8525-397cd178f238</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CARLOS JULIO GONZALEZ PATINO</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>16070633</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>943e8017-9c8c-423e-b3a4-557cbeb5e2b3</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES PATINO GAVIRIA</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1037602858</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>d8bf2e63-64c7-40c2-b57c-e92c533f4541</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES PATINO MEDINA</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,200 +478,200 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1110508660</t>
+          <t>4513697</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>f91148d1-ec55-4752-a63d-f4f65d506b0f</t>
+          <t>e87160f0-d751-4257-93bc-0cedad732a1d</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CARLOS  MOLANO PATINO</t>
+          <t>HECTOR FABIO GUTIERREZ RAMIREZ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CARLOS PATINO</t>
+          <t>HECTOR FABIO RAMIREZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.67%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR, LAVADO DE ACTIVOS</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+          <t>https://www.fiscalia.gov.co/colombia/lavado-de-activos/desarticulada-red-delictiva-dedicada-a-la-falsificacion-y-distribucion-de-moneda-y-billetes-de-loteria-a-gran-escala/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>79782900</t>
+          <t>1116238452</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5cecd100-6ea6-4011-b8d6-75aa949a0cef</t>
+          <t>862528c7-b454-46e6-82f1-951e1fc5fdd9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO PATINO GOMEZ</t>
+          <t>HECTOR FABIO TORO RAMIREZ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CARLOS PATINO</t>
+          <t>HECTOR FABIO RAMIREZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR, LAVADO DE ACTIVOS</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+          <t>https://www.fiscalia.gov.co/colombia/lavado-de-activos/desarticulada-red-delictiva-dedicada-a-la-falsificacion-y-distribucion-de-moneda-y-billetes-de-loteria-a-gran-escala/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1015995474</t>
+          <t>10143284</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>87096349-59aa-4e18-a4b3-3739e0b8f9d3</t>
+          <t>0dff7ee0-8f81-4649-a5a3-dcbe077470a0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO CEBALLOS PATINO</t>
+          <t>HECTOR FABIO GIRALDO RAMIREZ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CARLOS PATINO</t>
+          <t>HECTOR FABIO RAMIREZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR, LAVADO DE ACTIVOS</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+          <t>https://www.fiscalia.gov.co/colombia/lavado-de-activos/desarticulada-red-delictiva-dedicada-a-la-falsificacion-y-distribucion-de-moneda-y-billetes-de-loteria-a-gran-escala/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1127246130</t>
+          <t>71784179</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>efdd7814-d9ec-4b7e-a577-80b9a39b893c</t>
+          <t>86442c54-04bc-46dd-baeb-588669fefac7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CARLOS SAUL ORDONEZ PATINO</t>
+          <t>HECTOR FABIO GARZON RAMIREZ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CARLOS PATINO</t>
+          <t>HECTOR FABIO RAMIREZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR, LAVADO DE ACTIVOS</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+          <t>https://www.fiscalia.gov.co/colombia/lavado-de-activos/desarticulada-red-delictiva-dedicada-a-la-falsificacion-y-distribucion-de-moneda-y-billetes-de-loteria-a-gran-escala/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10186239</t>
+          <t>1110508660</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8d5b5c44-4bf1-41bf-b64d-682ff1c66f9a</t>
+          <t>f91148d1-ec55-4752-a63d-f4f65d506b0f</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JOSE CARLOS PATINO TORRES</t>
+          <t>CARLOS  MOLANO PATINO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.67%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1024597625</t>
+          <t>79758199</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1ccd17c1-b7c0-48ba-a5b1-f35dc84fe985</t>
+          <t>03d3b004-0384-4441-9585-a53ad5ded632</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CARLOS DANIEL PATINO ALVAREZ</t>
+          <t>ALEXANDER  AMADO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CARLOS PATINO</t>
+          <t>JAVIER ALEXANDER ORTIZ AMADO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -743,29 +743,29 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+          <t>SECUESTRO</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/identificados-presuntos-integrantes-del-tren-de-aragua-que-habrian-secuestrado-y-torturado-a-comerciante-venezolano-en-norte-de-santander/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12753448</t>
+          <t>79782900</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>f5360ff2-d0aa-48b0-8023-818c5b49f4ba</t>
+          <t>5cecd100-6ea6-4011-b8d6-75aa949a0cef</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO GARCIA PATINO</t>
+          <t>CARLOS EDUARDO PATINO GOMEZ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -807,12 +807,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1090450095</t>
+          <t>1015995474</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1648e2b7-409f-434c-8257-1d56c09930c4</t>
+          <t>87096349-59aa-4e18-a4b3-3739e0b8f9d3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO PATINO PABON</t>
+          <t>CARLOS ALBERTO CEBALLOS PATINO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -854,12 +854,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1044604037</t>
+          <t>1127246130</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>442d112b-8e1f-4cc7-aa09-dacd39b3226b</t>
+          <t>efdd7814-d9ec-4b7e-a577-80b9a39b893c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JUAN CARLOS MARTINEZ PATINO</t>
+          <t>CARLOS SAUL ORDONEZ PATINO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -901,12 +901,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>80773120</t>
+          <t>10186239</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>d238de83-6673-4098-9eb3-d082f1433d5f</t>
+          <t>8d5b5c44-4bf1-41bf-b64d-682ff1c66f9a</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CARLOS HERNAN LOPEZ PATINO</t>
+          <t>JOSE CARLOS PATINO TORRES</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -948,12 +948,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1039469469</t>
+          <t>1024597625</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>082cce38-b173-4cea-b792-34ef3d236930</t>
+          <t>1ccd17c1-b7c0-48ba-a5b1-f35dc84fe985</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JUAN CARLOS RIOS PATINO</t>
+          <t>CARLOS DANIEL PATINO ALVAREZ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -995,12 +995,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1144029836</t>
+          <t>12753448</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8012b3e9-2e46-472a-8991-fddc1bf2847e</t>
+          <t>f5360ff2-d0aa-48b0-8023-818c5b49f4ba</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES CABAL PATINO</t>
+          <t>CARLOS EDUARDO GARCIA PATINO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1042,12 +1042,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1002567379</t>
+          <t>1090450095</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>c98b569f-90c3-4f40-be02-3f4e8368a86f</t>
+          <t>1648e2b7-409f-434c-8257-1d56c09930c4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CARLOS MANUEL BOTERO PATINO</t>
+          <t>CARLOS EDUARDO PATINO PABON</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1089,12 +1089,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1020826607</t>
+          <t>1044604037</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2ef0b0a0-c7e2-4174-be71-484f772fc156</t>
+          <t>442d112b-8e1f-4cc7-aa09-dacd39b3226b</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES PATINO LOPEZ</t>
+          <t>JUAN CARLOS MARTINEZ PATINO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1136,12 +1136,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10030664</t>
+          <t>80773120</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>58efc384-cd5d-45ea-82e3-a6f096e6da99</t>
+          <t>d238de83-6673-4098-9eb3-d082f1433d5f</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CARLOS ANIBAL PATINO RAMIREZ</t>
+          <t>CARLOS HERNAN LOPEZ PATINO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1183,12 +1183,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>79945824</t>
+          <t>1039469469</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>a4319a5a-7178-4826-a054-1fc82ba3b2a9</t>
+          <t>082cce38-b173-4cea-b792-34ef3d236930</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CARLOS AUREL PATINO ECHEVERRI</t>
+          <t>JUAN CARLOS RIOS PATINO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1230,12 +1230,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>80822149</t>
+          <t>1144029836</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>c2781408-6e0f-4957-adef-cf5b45dbf7ba</t>
+          <t>8012b3e9-2e46-472a-8991-fddc1bf2847e</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LUIS CARLOS TOBAR PATINO</t>
+          <t>CARLOS ANDRES CABAL PATINO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1277,12 +1277,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>80255197</t>
+          <t>1002567379</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>deab6738-62ca-4f49-9299-4766f98097ca</t>
+          <t>c98b569f-90c3-4f40-be02-3f4e8368a86f</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JUAN CARLOS CARDENAS PATINO</t>
+          <t>CARLOS MANUEL BOTERO PATINO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1324,12 +1324,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1004624263</t>
+          <t>1020826607</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>e4769e5f-b184-4d9e-a325-277bca59ba68</t>
+          <t>2ef0b0a0-c7e2-4174-be71-484f772fc156</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO MOLINA PATINO</t>
+          <t>CARLOS ANDRES PATINO LOPEZ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1371,12 +1371,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1042854584</t>
+          <t>10030664</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>28e60d16-7821-414c-81c0-08e9a0119af7</t>
+          <t>58efc384-cd5d-45ea-82e3-a6f096e6da99</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CARLOS ALFONSO CALABRIA PATINO</t>
+          <t>CARLOS ANIBAL PATINO RAMIREZ</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1418,12 +1418,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>80011661</t>
+          <t>79945824</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>e9297d63-8a8a-4bad-a6eb-b6e0c95f5905</t>
+          <t>a4319a5a-7178-4826-a054-1fc82ba3b2a9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CARLOS AUGUSTO NEIRA PATINO</t>
+          <t>CARLOS AUREL PATINO ECHEVERRI</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1465,12 +1465,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1024571384</t>
+          <t>80822149</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>b96bb9c7-c3fb-490d-9a40-8c42237f0bf0</t>
+          <t>c2781408-6e0f-4957-adef-cf5b45dbf7ba</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JUAN CARLOS GALEANO PATINO</t>
+          <t>LUIS CARLOS TOBAR PATINO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1512,12 +1512,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1010093562</t>
+          <t>80255197</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>dbf6f035-2e66-492e-a3f3-72c7e67f7077</t>
+          <t>deab6738-62ca-4f49-9299-4766f98097ca</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>JUAN CARLOS GOMEZ PATINO</t>
+          <t>JUAN CARLOS CARDENAS PATINO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1559,12 +1559,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1090987718</t>
+          <t>1004624263</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8287037c-603c-4952-805c-1705e21b244b</t>
+          <t>e4769e5f-b184-4d9e-a325-277bca59ba68</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CARLOS MARIO PATINO RIOS</t>
+          <t>CARLOS ALBERTO MOLINA PATINO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1606,12 +1606,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>71291775</t>
+          <t>1042854584</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>b2296f2e-0f8b-477b-935e-11d5eba248f5</t>
+          <t>28e60d16-7821-414c-81c0-08e9a0119af7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CARLOS AUGUSTO RUIZ PATINO</t>
+          <t>CARLOS ALFONSO CALABRIA PATINO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1653,12 +1653,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>71384730</t>
+          <t>80011661</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>012dd7e3-0710-4ebd-982e-cef32ee80eb3</t>
+          <t>e9297d63-8a8a-4bad-a6eb-b6e0c95f5905</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES BOTERO PATINO</t>
+          <t>CARLOS AUGUSTO NEIRA PATINO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1700,12 +1700,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>88252671</t>
+          <t>1024571384</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>72b28ae6-85a3-4d13-a271-2fb8dc5a82a8</t>
+          <t>b96bb9c7-c3fb-490d-9a40-8c42237f0bf0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CARLOS MANUEL PATINO MACHADO</t>
+          <t>JUAN CARLOS GALEANO PATINO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1747,12 +1747,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1010245307</t>
+          <t>1010093562</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3cb42c84-08b4-4a71-a7cc-7f75f7fccadf</t>
+          <t>dbf6f035-2e66-492e-a3f3-72c7e67f7077</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO GUEVARA PATINO</t>
+          <t>JUAN CARLOS GOMEZ PATINO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1794,12 +1794,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1042852549</t>
+          <t>1090987718</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>b151199f-9222-49ec-8c73-831552ad6c0e</t>
+          <t>8287037c-603c-4952-805c-1705e21b244b</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CARLOS MIGUEL CALABRIA PATINO</t>
+          <t>CARLOS MARIO PATINO RIOS</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1841,12 +1841,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1148701468</t>
+          <t>71291775</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2d56837a-4ad2-4f10-888b-56b7643cdc27</t>
+          <t>b2296f2e-0f8b-477b-935e-11d5eba248f5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES PATINO HERNANDEZ</t>
+          <t>CARLOS AUGUSTO RUIZ PATINO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1888,12 +1888,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1097402784</t>
+          <t>71384730</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>eb540e85-d60b-4b2a-b00d-0df6ceda8d6f</t>
+          <t>012dd7e3-0710-4ebd-982e-cef32ee80eb3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CARLOS ARTURO OSPINA PATINO</t>
+          <t>CARLOS ANDRES BOTERO PATINO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1935,12 +1935,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1151955585</t>
+          <t>88252671</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>dc8585e3-9062-4ff9-a8ea-776457d74671</t>
+          <t>72b28ae6-85a3-4d13-a271-2fb8dc5a82a8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO CRUZ PATINO</t>
+          <t>CARLOS MANUEL PATINO MACHADO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1045680502</t>
+          <t>1010245307</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>715bd418-acda-4388-8e1d-1275573d19b0</t>
+          <t>3cb42c84-08b4-4a71-a7cc-7f75f7fccadf</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES PATINO CABRERA</t>
+          <t>CARLOS EDUARDO GUEVARA PATINO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2029,12 +2029,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1102887727</t>
+          <t>1042852549</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>48c7c54f-628a-4c8b-909d-5564775aacd5</t>
+          <t>b151199f-9222-49ec-8c73-831552ad6c0e</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CARLOS LEONARDO MONROY PATINO</t>
+          <t>CARLOS MIGUEL CALABRIA PATINO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2076,12 +2076,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1095838786</t>
+          <t>1148701468</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>839aa280-4e7e-4b8b-914f-9a066b0586b0</t>
+          <t>2d56837a-4ad2-4f10-888b-56b7643cdc27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO PATINO BECERRA</t>
+          <t>CARLOS ANDRES PATINO HERNANDEZ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2123,12 +2123,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>94418174</t>
+          <t>1097402784</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>035f053a-5176-4e7c-b119-31851513a868</t>
+          <t>eb540e85-d60b-4b2a-b00d-0df6ceda8d6f</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JUAN CARLOS RUIZ PATINO</t>
+          <t>CARLOS ARTURO OSPINA PATINO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2170,12 +2170,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>19465846</t>
+          <t>1151955585</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>85a42ffd-7730-4caf-af61-27b607744eff</t>
+          <t>dc8585e3-9062-4ff9-a8ea-776457d74671</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO PATINO VARGAS</t>
+          <t>CARLOS EDUARDO CRUZ PATINO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1057582624</t>
+          <t>1045680502</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>35a3aa4a-313f-4e83-b743-136ce931c0a2</t>
+          <t>715bd418-acda-4388-8e1d-1275573d19b0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LUIS CARLOS PATINO LAGOS</t>
+          <t>CARLOS ANDRES PATINO CABRERA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2264,12 +2264,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8064063</t>
+          <t>1102887727</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dfafa730-2393-4afc-8302-0c7cab9c4f36</t>
+          <t>48c7c54f-628a-4c8b-909d-5564775aacd5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO PATINO LOPEZ</t>
+          <t>CARLOS LEONARDO MONROY PATINO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>16723021</t>
+          <t>1095838786</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>a6efd779-ce6c-4e90-b17d-0d74663612b2</t>
+          <t>839aa280-4e7e-4b8b-914f-9a066b0586b0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>JUAN CARLOS PATINO RODRIGUEZ</t>
+          <t>CARLOS EDUARDO PATINO BECERRA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2358,12 +2358,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14473070</t>
+          <t>94418174</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>022c85fa-855b-4156-b7fd-74676137d193</t>
+          <t>035f053a-5176-4e7c-b119-31851513a868</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>JUAN CARLOS MURILLO PATINO</t>
+          <t>JUAN CARLOS RUIZ PATINO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2405,12 +2405,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1021803274</t>
+          <t>19465846</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>b92c0ad2-07ca-472d-831f-7d230d58dda3</t>
+          <t>85a42ffd-7730-4caf-af61-27b607744eff</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>JEAN CARLOS MONTOYA PATINO</t>
+          <t>CARLOS EDUARDO PATINO VARGAS</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2452,12 +2452,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1035833688</t>
+          <t>1057582624</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15ccf04c-4a93-4c65-9469-456dac73354c</t>
+          <t>35a3aa4a-313f-4e83-b743-136ce931c0a2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES MUNOZ PATINO</t>
+          <t>LUIS CARLOS PATINO LAGOS</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2499,12 +2499,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1014185154</t>
+          <t>8064063</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1cba96cc-1ae8-471c-bfac-3d1419e0c4f3</t>
+          <t>dfafa730-2393-4afc-8302-0c7cab9c4f36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES PATINO GIL</t>
+          <t>CARLOS ALBERTO PATINO LOPEZ</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2546,12 +2546,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1010094927</t>
+          <t>16723021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6b660e90-a6ef-43e9-9811-7ff7dc1d17cb</t>
+          <t>a6efd779-ce6c-4e90-b17d-0d74663612b2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CARLOS DANIEL ORTIZ PATINO</t>
+          <t>JUAN CARLOS PATINO RODRIGUEZ</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2593,12 +2593,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>98659911</t>
+          <t>14473070</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0104cbf2-9469-4d99-9914-460fcf022ab3</t>
+          <t>022c85fa-855b-4156-b7fd-74676137d193</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>JUAN CARLOS PATINO MANRIQUE</t>
+          <t>JUAN CARLOS MURILLO PATINO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2640,12 +2640,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>14136606</t>
+          <t>1021803274</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2e00cc48-3a00-4bce-927b-45a5682e4c3c</t>
+          <t>b92c0ad2-07ca-472d-831f-7d230d58dda3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO PATINO HERRERA</t>
+          <t>JEAN CARLOS MONTOYA PATINO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2687,12 +2687,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1020806800</t>
+          <t>1035833688</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>bd433edd-5c13-41f9-96e7-7644a1c5a0db</t>
+          <t>15ccf04c-4a93-4c65-9469-456dac73354c</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES BARRETO PATINO</t>
+          <t>CARLOS ANDRES MUNOZ PATINO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2734,12 +2734,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10117792</t>
+          <t>1014185154</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3cdeb45d-1610-42db-9a54-7711c2b65da0</t>
+          <t>1cba96cc-1ae8-471c-bfac-3d1419e0c4f3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JUAN CARLOS JARAMILLO PATINO</t>
+          <t>CARLOS ANDRES PATINO GIL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2781,12 +2781,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1013687267</t>
+          <t>1010094927</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4cbdc802-05d1-4806-a935-3644f5ce8b8c</t>
+          <t>6b660e90-a6ef-43e9-9811-7ff7dc1d17cb</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CARLOS ARTURO PATINO MARIN</t>
+          <t>CARLOS DANIEL ORTIZ PATINO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2828,12 +2828,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1019102664</t>
+          <t>98659911</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4efc391c-e2a4-4d1b-9763-0bf3bac8a803</t>
+          <t>0104cbf2-9469-4d99-9914-460fcf022ab3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CARLOS JULIO PATINO SUAREZ</t>
+          <t>JUAN CARLOS PATINO MANRIQUE</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2875,12 +2875,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1057609620</t>
+          <t>14136606</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2674895b-803f-4d30-9f8a-1e6d32d02595</t>
+          <t>2e00cc48-3a00-4bce-927b-45a5682e4c3c</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CARLOS ALFREDO PATINO MORENO</t>
+          <t>CARLOS ALBERTO PATINO HERRERA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2922,12 +2922,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1080266516</t>
+          <t>1020806800</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2969fcac-6e7a-4adb-86ae-e3dfd272e3d1</t>
+          <t>bd433edd-5c13-41f9-96e7-7644a1c5a0db</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES JURADO PATINO</t>
+          <t>CARLOS ANDRES BARRETO PATINO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2969,12 +2969,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7730808</t>
+          <t>10117792</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2aacb798-d57e-42f7-bac6-1a7077720666</t>
+          <t>3cdeb45d-1610-42db-9a54-7711c2b65da0</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>JUAN CARLOS PATINO VERGEL</t>
+          <t>JUAN CARLOS JARAMILLO PATINO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3016,12 +3016,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1098817537</t>
+          <t>1013687267</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>04d0ea15-3d7e-447d-b937-d0d0bfe4b9f4</t>
+          <t>4cbdc802-05d1-4806-a935-3644f5ce8b8c</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES PATINO ROMERO</t>
+          <t>CARLOS ARTURO PATINO MARIN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3063,12 +3063,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1016110073</t>
+          <t>1019102664</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>712158aa-4bb7-4b80-9a3b-2937048b133a</t>
+          <t>4efc391c-e2a4-4d1b-9763-0bf3bac8a803</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CARLOS DANIEL PATINO GOMEZ</t>
+          <t>CARLOS JULIO PATINO SUAREZ</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3110,12 +3110,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1094909424</t>
+          <t>1057609620</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>cb523290-1fe8-454c-b312-45905a6e38de</t>
+          <t>2674895b-803f-4d30-9f8a-1e6d32d02595</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>JOSE CARLOS PATINO BAQUERO</t>
+          <t>CARLOS ALFREDO PATINO MORENO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3157,12 +3157,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1000707828</t>
+          <t>1080266516</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>febf0db0-b921-457b-a86f-88a16b135420</t>
+          <t>2969fcac-6e7a-4adb-86ae-e3dfd272e3d1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CARLOS FELIPE PATINO ALVAREZ</t>
+          <t>CARLOS ANDRES JURADO PATINO</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3204,12 +3204,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1017156499</t>
+          <t>7730808</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>d62cb0dc-6a84-4cd2-be5d-7a043a82b496</t>
+          <t>2aacb798-d57e-42f7-bac6-1a7077720666</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CARLOS MARIO ARBOLEDA PATINO</t>
+          <t>JUAN CARLOS PATINO VERGEL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3251,12 +3251,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1233190969</t>
+          <t>1098817537</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>a6de2b59-c436-4249-9047-1c5fa8f01b6c</t>
+          <t>04d0ea15-3d7e-447d-b937-d0d0bfe4b9f4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES CUASTUMAL PATINO</t>
+          <t>CARLOS ANDRES PATINO ROMERO</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3298,12 +3298,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1020487686</t>
+          <t>1016110073</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0c1f2a63-16fc-476f-8c4d-64bc7f0a3c77</t>
+          <t>712158aa-4bb7-4b80-9a3b-2937048b133a</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CARLOS MARIO PATINO BETANCUR</t>
+          <t>CARLOS DANIEL PATINO GOMEZ</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3345,12 +3345,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1106768796</t>
+          <t>1094909424</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>eaca9f45-f36c-428c-8525-397cd178f238</t>
+          <t>cb523290-1fe8-454c-b312-45905a6e38de</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CARLOS JULIO GONZALEZ PATINO</t>
+          <t>JOSE CARLOS PATINO BAQUERO</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3392,12 +3392,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16070633</t>
+          <t>1000707828</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>943e8017-9c8c-423e-b3a4-557cbeb5e2b3</t>
+          <t>febf0db0-b921-457b-a86f-88a16b135420</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CARLOS ANDRES PATINO GAVIRIA</t>
+          <t>CARLOS FELIPE PATINO ALVAREZ</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3439,45 +3439,280 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>1017156499</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>d62cb0dc-6a84-4cd2-be5d-7a043a82b496</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CARLOS MARIO ARBOLEDA PATINO</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1233190969</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>a6de2b59-c436-4249-9047-1c5fa8f01b6c</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES CUASTUMAL PATINO</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1020487686</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0c1f2a63-16fc-476f-8c4d-64bc7f0a3c77</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CARLOS MARIO PATINO BETANCUR</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1106768796</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>eaca9f45-f36c-428c-8525-397cd178f238</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CARLOS JULIO GONZALEZ PATINO</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>16070633</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>943e8017-9c8c-423e-b3a4-557cbeb5e2b3</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES PATINO GAVIRIA</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>1037602858</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>d8bf2e63-64c7-40c2-b57c-e92c533f4541</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>CARLOS ANDRES PATINO MEDINA</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>CARLOS PATINO</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>CARLOS PATINO</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>PORTE DE ARMAS, TERRORISMO, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
         <is>
           <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-en-centro-carcelario-dos-presuntos-explosivistas-de-las-disidencias-de-las-farc-que-estarian-implicados-en-ataques-terroristas-en-cauca/</t>
         </is>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,282 +478,141 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1070921267</t>
+          <t>1020832479</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>901271b3-b60d-433e-aea6-da0125ff7307</t>
+          <t>f24bdbbb-bc4d-42cb-9563-f59202e9722c</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DIEGO ESTEBAN VALDERRAMA CASTELLANOS</t>
+          <t>MANUELA  SEPULVEDA GIRALDO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DIEGO ESTEBAN VALDERRAMA</t>
+          <t>SEPULVEDA GIRALDO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.67%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/condenados-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-florencia-caqueta/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/condenados-a-mas-de-35-anos-de-prision-responsables-del-crimen-de-un-joven-en-medellin/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1016097284</t>
+          <t>1000048835</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5524936b-7bd4-444c-898f-cf997b9a8829</t>
+          <t>700e4197-c048-45c1-8883-9e5b7af45131</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JHON ALEJANDRO HUERFANO CALDERON</t>
+          <t>ANDRES FELIPE SEPULVEDA GIRALDO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JHON ALEJANDRO CALDERON</t>
+          <t>SEPULVEDA GIRALDO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/condenados-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-florencia-caqueta/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/condenados-a-mas-de-35-anos-de-prision-responsables-del-crimen-de-un-joven-en-medellin/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1143379884</t>
+          <t>1035222415</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>78630818-8795-41a0-9845-b328037e4048</t>
+          <t>159edcf3-d654-4226-8d2a-6d8ce52a470e</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JAIRO ANDRES SOTO GIRALDO</t>
+          <t>JHAN CARLOS SEPULVEDA GIRALDO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JAIRO ANDRES GIRALDO</t>
+          <t>SEPULVEDA GIRALDO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+          <t>CONCIERTO PARA DELINQUIR</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/condenados-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-florencia-caqueta/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1037614932</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>f23fed33-76cc-4b5d-abb7-f73a9ed8bde6</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ANDRES  GIRALDO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>JAIRO ANDRES GIRALDO</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>66.67%</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/condenados-integrantes-de-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-florencia-caqueta/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1098687214</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>65c1380b-09ef-45d9-976d-39e75f9046cc</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>EVER DANIEL CASTRO RODRIGUEZ</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>EVER CASTRO</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/presunto-integrante-de-las-disidencias-de-las-farc-fue-judicializado-por-acciones-armadas-contra-firmantes-de-paz-en-meta/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1036630586</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>e69cbb14-d0f7-4dba-aabf-296d0f81214b</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>EVER ANTONIO CASTRO ALVAREZ</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>EVER CASTRO</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/presunto-integrante-de-las-disidencias-de-las-farc-fue-judicializado-por-acciones-armadas-contra-firmantes-de-paz-en-meta/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/condenados-a-mas-de-35-anos-de-prision-responsables-del-crimen-de-un-joven-en-medellin/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,147 +472,6 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>URL_NOTICIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1020832479</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>f24bdbbb-bc4d-42cb-9563-f59202e9722c</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MANUELA  SEPULVEDA GIRALDO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SEPULVEDA GIRALDO</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>66.67%</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/condenados-a-mas-de-35-anos-de-prision-responsables-del-crimen-de-un-joven-en-medellin/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1000048835</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>700e4197-c048-45c1-8883-9e5b7af45131</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ANDRES FELIPE SEPULVEDA GIRALDO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SEPULVEDA GIRALDO</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/condenados-a-mas-de-35-anos-de-prision-responsables-del-crimen-de-un-joven-en-medellin/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1035222415</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>159edcf3-d654-4226-8d2a-6d8ce52a470e</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>JHAN CARLOS SEPULVEDA GIRALDO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SEPULVEDA GIRALDO</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/condenados-a-mas-de-35-anos-de-prision-responsables-del-crimen-de-un-joven-en-medellin/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,6 +475,711 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1541519</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>9c1c3541-78c6-4998-9b70-a4a2ddc5ee32</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FRANCISCO  MARTINEZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WALTER FRANCISCO MARTINEZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ENRIQUECIMIENTO ILICITO, CONTRABANDO, CONCIERTO PARA DELINQUIR, LAVADO DE ACTIVOS</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-presunto-integrante-de-red-trasnacional-senalado-de-ingresar-ropa-femenina-y-accesorios-de-contrabando-al-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1007017418</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>9fb66c9f-4766-4608-a4f4-6d72361ccc18</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PABLO FRANCISCO SOLANO DAVILA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PABLO SOLANO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/cuatro-hombres-que-estarian-involucrados-en-el-almacenamiento-de-estupefacientes-en-paipa-boyaca-fueron-asegurados/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1098825450</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7a482a5c-733f-4b56-9260-98df445edd12</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>JUAN PABLO SOLANO SANTAMARIA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PABLO SOLANO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/cuatro-hombres-que-estarian-involucrados-en-el-almacenamiento-de-estupefacientes-en-paipa-boyaca-fueron-asegurados/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1129582157</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>14e68509-8f47-48d7-a4a5-b30597fcb562</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>JUAN PABLO MEJIA SOLANO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PABLO SOLANO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/cuatro-hombres-que-estarian-involucrados-en-el-almacenamiento-de-estupefacientes-en-paipa-boyaca-fueron-asegurados/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1192804224</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>857adfcf-4137-4c09-9ffb-a10d6defde37</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>JUAN PABLO SOLANO ROMERO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PABLO SOLANO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/cuatro-hombres-que-estarian-involucrados-en-el-almacenamiento-de-estupefacientes-en-paipa-boyaca-fueron-asegurados/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1013612006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>a78890a5-e3c6-4c2c-8798-fa466d9d3941</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>JUAN PABLO SOLANO POLOCHE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PABLO SOLANO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/cuatro-hombres-que-estarian-involucrados-en-el-almacenamiento-de-estupefacientes-en-paipa-boyaca-fueron-asegurados/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1032418724</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4a8dbe3e-a07b-4018-a101-06bcd1613a1c</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PABLO ENRIQUE NEMOCON SOLANO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PABLO SOLANO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/cuatro-hombres-que-estarian-involucrados-en-el-almacenamiento-de-estupefacientes-en-paipa-boyaca-fueron-asegurados/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1069715356</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1526edc8-1d66-4fef-86ef-76f94603381f</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>JUAN PABLO SOLANO ROJAS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PABLO SOLANO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/cuatro-hombres-que-estarian-involucrados-en-el-almacenamiento-de-estupefacientes-en-paipa-boyaca-fueron-asegurados/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1023959028</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>d6a3538d-6e1b-45b9-a377-c801772fc5bb</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>JUAN PABLO SOLANO RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PABLO SOLANO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/cuatro-hombres-que-estarian-involucrados-en-el-almacenamiento-de-estupefacientes-en-paipa-boyaca-fueron-asegurados/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1130264987</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>e718ac5d-4cc4-46f2-9ff7-f984910b047a</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PABLO YESID SOLANO NIEBLES</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PABLO SOLANO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/cuatro-hombres-que-estarian-involucrados-en-el-almacenamiento-de-estupefacientes-en-paipa-boyaca-fueron-asegurados/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1032488711</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>9a93a87f-9e86-43b9-8eee-7d8b433f5a01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>JUAN PABLO SOLANO LOPEZ</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PABLO SOLANO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/cuatro-hombres-que-estarian-involucrados-en-el-almacenamiento-de-estupefacientes-en-paipa-boyaca-fueron-asegurados/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1144049733</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>8f9047a3-bc03-45f3-afda-cc5cfb5e6c22</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PABLO CESAR SOLANO CERTUCHE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PABLO SOLANO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/cuatro-hombres-que-estarian-involucrados-en-el-almacenamiento-de-estupefacientes-en-paipa-boyaca-fueron-asegurados/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1122810415</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>eb472746-d6e9-455d-a674-c72512b38973</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>JUAN PABLO FIGUEROA SOLANO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PABLO SOLANO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/cuatro-hombres-que-estarian-involucrados-en-el-almacenamiento-de-estupefacientes-en-paipa-boyaca-fueron-asegurados/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1010005749</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>790adf51-d830-4860-947f-3915923b4ca0</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>JUAN PABLO PALACIOS SOLANO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PABLO SOLANO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/cuatro-hombres-que-estarian-involucrados-en-el-almacenamiento-de-estupefacientes-en-paipa-boyaca-fueron-asegurados/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1075312454</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>568e6c5b-da6d-40b8-b982-f6ae250178e7</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PABLO CESAR SARMIENTOSOLANO SOLANO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PABLO SOLANO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/cuatro-hombres-que-estarian-involucrados-en-el-almacenamiento-de-estupefacientes-en-paipa-boyaca-fueron-asegurados/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,6 +475,523 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1072643902</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dd57fbd0-f421-4020-a3d8-6f59a7fc65df</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BRAYAN DAVID LOPEZ ESPINOSA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DAVID LOPEZ ESPINOSA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-10-personas-presuntamente-involucradas-en-el-trafico-local-de-estupefacientes-en-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1010144012</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c3203de5-a328-4d2d-95e5-51621253fa07</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>JESUS DAVID LOPEZ ESPINOSA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DAVID LOPEZ ESPINOSA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-10-personas-presuntamente-involucradas-en-el-trafico-local-de-estupefacientes-en-valle-del-cauca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6102721</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>23552053-5af5-4b03-b754-e1e910f36bcb</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>JAIME ANDRES RODRIGUEZ CHOACHI</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/golpe-a-los-olivares-organizacion-delincuencial-senalada-de-dinamizar-el-trafico-local-de-estupefacientes-en-el-sur-de-bogota/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1015397737</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>bd56b35e-d714-4b4e-b814-7a29cc5b756b</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES CORTES</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES CARDENAS CORTES</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/golpe-a-los-olivares-organizacion-delincuencial-senalada-de-dinamizar-el-trafico-local-de-estupefacientes-en-el-sur-de-bogota/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1000746562</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>28349d43-9153-4b51-8e68-640448478023</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>YEFERSON  GOMEZ ORTIZ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>YEFERSON GOMEZ</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/golpe-a-los-olivares-organizacion-delincuencial-senalada-de-dinamizar-el-trafico-local-de-estupefacientes-en-el-sur-de-bogota/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1037650258</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fab95fbe-ae8b-446e-a3ce-86760f144a14</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>YEFERSON  GOMEZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>YEFERSON GOMEZ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/golpe-a-los-olivares-organizacion-delincuencial-senalada-de-dinamizar-el-trafico-local-de-estupefacientes-en-el-sur-de-bogota/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1093228757</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10989013-c595-414b-8b25-7d2ff0980b36</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>YEFERSON  GAITAN GOMEZ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>YEFERSON GOMEZ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/golpe-a-los-olivares-organizacion-delincuencial-senalada-de-dinamizar-el-trafico-local-de-estupefacientes-en-el-sur-de-bogota/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1045172460</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>05505c78-5e87-42b9-a758-9acb63f25360</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>YEFERSON  GOMEZ LOPEZ</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>YEFERSON GOMEZ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/golpe-a-los-olivares-organizacion-delincuencial-senalada-de-dinamizar-el-trafico-local-de-estupefacientes-en-el-sur-de-bogota/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1214728330</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>aea69640-623b-4996-93e3-afc3e29c9ac8</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>YEFERSON  OSORIO GOMEZ</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>YEFERSON GOMEZ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/golpe-a-los-olivares-organizacion-delincuencial-senalada-de-dinamizar-el-trafico-local-de-estupefacientes-en-el-sur-de-bogota/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1013602005</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>61cbf282-9928-4b2a-a188-64ce314b3ea5</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>YEFERSON ARIEL CABRERA GOMEZ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>YEFERSON GOMEZ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/golpe-a-los-olivares-organizacion-delincuencial-senalada-de-dinamizar-el-trafico-local-de-estupefacientes-en-el-sur-de-bogota/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1002793100</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>b84ae00f-580a-4f1a-a3e3-83b67760d2e6</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>YEFERSON DAVID GOMEZ MUNOZ</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>YEFERSON GOMEZ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/golpe-a-los-olivares-organizacion-delincuencial-senalada-de-dinamizar-el-trafico-local-de-estupefacientes-en-el-sur-de-bogota/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,53 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>URL_NOTICIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1002543298</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>b6929cd2-a3f5-497a-9e83-b3c37bb7935b</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DANIEL  MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DANIEL FERNANDO MARTINEZ FALLA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ADMINISTRACION PUBLICA, PREVARICATO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-exalcalde-de-neiva-otros-directivos-por-su-presunta-responsabilidad-en-la-modificacion-irregular-del-plan-de-ordenamiento-territorial/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,53 +472,6 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>URL_NOTICIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1002543298</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>b6929cd2-a3f5-497a-9e83-b3c37bb7935b</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🟡 ALERTA BAJA (2 Palabras)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>DANIEL  MARTINEZ</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>DANIEL FERNANDO MARTINEZ FALLA</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ADMINISTRACION PUBLICA, PREVARICATO</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializado-exalcalde-de-neiva-otros-directivos-por-su-presunta-responsabilidad-en-la-modificacion-irregular-del-plan-de-ordenamiento-territorial/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,53 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>URL_NOTICIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1128447084</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>6ace72f6-75c0-475e-8b14-507b322705b3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ANDRES  TAMAYO GONZALEZ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HERBER ANDRES TAMAYO GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SECUESTRO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializados-hombres-senalados-de-citar-mediante-enganos-a-un-comerciante-para-secuestrarlo-extorsionar-a-su-familia-y-arrebatarle-sus-pertenencias/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -478,12 +478,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1128447084</t>
+          <t>1020491028</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6ace72f6-75c0-475e-8b14-507b322705b3</t>
+          <t>6a55d890-40a0-48b6-bc2c-3b3a41982c42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -493,12 +493,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ANDRES  TAMAYO GONZALEZ</t>
+          <t>PATRICIA  QUINTERO GOMEZ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HERBER ANDRES TAMAYO GONZALEZ</t>
+          <t>SANDRA PATRICIA QUINTERO GOMEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -508,17 +508,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SECUESTRO</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializados-hombres-senalados-de-citar-mediante-enganos-a-un-comerciante-para-secuestrarlo-extorsionar-a-su-familia-y-arrebatarle-sus-pertenencias/</t>
+          <t>https://www.fiscalia.gov.co/colombia/seccionales/cuatro-personas-fueron-aseguradas-en-valle-del-cauca-por-presuntos-vinculos-con-trafico-local-de-narcoticos/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,53 +472,6 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>URL_NOTICIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1020491028</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>6a55d890-40a0-48b6-bc2c-3b3a41982c42</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>PATRICIA  QUINTERO GOMEZ</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SANDRA PATRICIA QUINTERO GOMEZ</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/seccionales/cuatro-personas-fueron-aseguradas-en-valle-del-cauca-por-presuntos-vinculos-con-trafico-local-de-narcoticos/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,288 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>URL_NOTICIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1140898036</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>74086757-7a55-4583-a4ed-089ff37c07e5</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN GONZALEZ PAYARES</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/afectada-red-delincuencial-senalada-de-comercializar-a-gran-escala-medicamentos-adulterados-para-el-cancer-la-diabetes-y-otras-enfermedades-de-alto-costo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1001969256</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>9f4e31c2-f614-4be1-94bf-2bdcfe28ff3a</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN GONZALEZ GOMEZ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/afectada-red-delincuencial-senalada-de-comercializar-a-gran-escala-medicamentos-adulterados-para-el-cancer-la-diabetes-y-otras-enfermedades-de-alto-costo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>51742216</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ed1cc5f5-16be-4904-8690-e45e1bcdf73c</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN RAMIREZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/afectada-red-delincuencial-senalada-de-comercializar-a-gran-escala-medicamentos-adulterados-para-el-cancer-la-diabetes-y-otras-enfermedades-de-alto-costo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>32634498</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>16b793b9-a915-4d3b-b5ed-f2d2441a1a55</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN GONZALEZ NULE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/afectada-red-delincuencial-senalada-de-comercializar-a-gran-escala-medicamentos-adulterados-para-el-cancer-la-diabetes-y-otras-enfermedades-de-alto-costo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>80235748</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7c54ba16-fac6-4f9c-ad0c-0c0fc77cc104</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL LOPEZ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL LOPEZ ORDONEZ</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/afectada-red-delincuencial-senalada-de-comercializar-a-gran-escala-medicamentos-adulterados-para-el-cancer-la-diabetes-y-otras-enfermedades-de-alto-costo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>385808</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>88f79e13-447b-44a0-b49d-65e8e48167b0</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MARIA EUGENIA DEL CARMEN ANEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/afectada-red-delincuencial-senalada-de-comercializar-a-gran-escala-medicamentos-adulterados-para-el-cancer-la-diabetes-y-otras-enfermedades-de-alto-costo/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,262 +478,262 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1140898036</t>
+          <t>1144080712</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>74086757-7a55-4583-a4ed-089ff37c07e5</t>
+          <t>bfc14249-531c-47ed-adea-361f539f71db</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MARIA DEL CARMEN GONZALEZ PAYARES</t>
+          <t>PEDRO ANTONIO ZAPE OROZCO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MARIA DEL CARMEN GONZALEZ</t>
+          <t>PEDRO ANTONIO OROZCO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
+          <t>SECUESTRO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/afectada-red-delincuencial-senalada-de-comercializar-a-gran-escala-medicamentos-adulterados-para-el-cancer-la-diabetes-y-otras-enfermedades-de-alto-costo/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializan-a-pareja-senalada-de-secuestrar-un-hombre-bajo-la-modalidad-de-falso-servicio-en-yopal-casanare/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1001969256</t>
+          <t>1094887627</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9f4e31c2-f614-4be1-94bf-2bdcfe28ff3a</t>
+          <t>4ca7514f-a0bb-4cc9-bfbf-732a554e6726</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MARIA DEL CARMEN GONZALEZ GOMEZ</t>
+          <t>ALEXANDER  ARIAS TORRES</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MARIA DEL CARMEN GONZALEZ</t>
+          <t>ALEXANDER ARIAS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.67%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/afectada-red-delincuencial-senalada-de-comercializar-a-gran-escala-medicamentos-adulterados-para-el-cancer-la-diabetes-y-otras-enfermedades-de-alto-costo/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>51742216</t>
+          <t>1035853738</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ed1cc5f5-16be-4904-8690-e45e1bcdf73c</t>
+          <t>1ec8679b-ace3-4054-a338-34bd12da640e</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MARIA DEL CARMEN RAMIREZ GONZALEZ</t>
+          <t>ALEXANDER  PELAEZ ARIAS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MARIA DEL CARMEN GONZALEZ</t>
+          <t>ALEXANDER ARIAS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.67%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/afectada-red-delincuencial-senalada-de-comercializar-a-gran-escala-medicamentos-adulterados-para-el-cancer-la-diabetes-y-otras-enfermedades-de-alto-costo/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>32634498</t>
+          <t>11255310</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16b793b9-a915-4d3b-b5ed-f2d2441a1a55</t>
+          <t>9dffecb3-2d88-431f-8e0d-5041e066da0a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MARIA DEL CARMEN GONZALEZ NULE</t>
+          <t>ALEXANDER  GONZALEZ ARIAS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MARIA DEL CARMEN GONZALEZ</t>
+          <t>ALEXANDER ARIAS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.67%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/afectada-red-delincuencial-senalada-de-comercializar-a-gran-escala-medicamentos-adulterados-para-el-cancer-la-diabetes-y-otras-enfermedades-de-alto-costo/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>80235748</t>
+          <t>1006072753</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7c54ba16-fac6-4f9c-ad0c-0c0fc77cc104</t>
+          <t>4f4b9aae-0729-472a-935a-1c19ce775363</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL LOPEZ</t>
+          <t>ALEXANDER  ARIAS PENA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL LOPEZ ORDONEZ</t>
+          <t>ALEXANDER ARIAS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.67%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/afectada-red-delincuencial-senalada-de-comercializar-a-gran-escala-medicamentos-adulterados-para-el-cancer-la-diabetes-y-otras-enfermedades-de-alto-costo/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>385808</t>
+          <t>1088279754</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88f79e13-447b-44a0-b49d-65e8e48167b0</t>
+          <t>5ab40325-b404-4fc1-9800-ae7b15f77bc0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔴 ALERTA CRÍTICA (4+ Palabras)</t>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MARIA EUGENIA DEL CARMEN ANEZ GONZALEZ</t>
+          <t>ALEXANDER  ARIAS HERNANDEZ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MARIA DEL CARMEN GONZALEZ</t>
+          <t>ALEXANDER ARIAS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -743,17 +743,2743 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CONCIERTO PARA DELINQUIR</t>
+          <t>ESTUPEFACIENTES</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/afectada-red-delincuencial-senalada-de-comercializar-a-gran-escala-medicamentos-adulterados-para-el-cancer-la-diabetes-y-otras-enfermedades-de-alto-costo/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>12102995</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>d8a326b8-94d2-46b5-a0a6-cfd16700f54d</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ALEXANDER  PINA ARIAS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1030597571</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>f8786ea0-16d9-440a-954e-9be91004119d</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>OSCAR ALEXANDER ARIAS GARZON</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1037670731</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>b77d28fb-6fae-4d35-8520-a62c7ecde359</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ALEXANDER ANTONIO CISNEROS ARIAS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1073239643</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>33f4a155-dd5f-4ac6-8724-3ff4b070074d</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DIEGO ALEXANDER GARCIA ARIAS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1128483794</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ff716ca8-fc43-4d78-a32a-347579d77f85</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BRYAN ALEXANDER ARIAS RESTREPO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1030571416</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>e901c98e-b7d4-4e23-820c-ba82305fee0b</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>JEISSON ALEXANDER ARIAS NAVARRO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1152702860</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>f4877b41-87ff-4443-b984-257cb0292609</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>KEVIN ALEXANDER ACOSTA ARIAS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1022398356</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2c890daf-2001-44cf-9598-58e1f3a397e2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>JHON ALEXANDER ZULUAGA ARIAS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1032490784</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>25c98273-a6b2-47e6-a7fc-03cef7b0b2ed</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>JIMMY ALEXANDER PULIDO ARIAS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1019023016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>8e878de9-8d2f-428a-92a9-e43eb756bf58</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FREDY ALEXANDER ARIAS VARELA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1007402025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>63fac67e-6d93-4a01-a79f-37e2fcba19b8</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ALEXIS ALEXANDER BEDOYA ARIAS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1007142374</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>f54bb91e-07b3-478d-924e-1bc2f9925467</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>YESID ALEXANDER CAICEDO ARIAS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1034657881</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>cb736349-9859-40aa-a614-965d62b833c6</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>RICHARD ALEXANDER RODRIGUEZ ARIAS</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1010180167</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>bb3b0bc5-e0f9-4020-85d1-ccb81fc64764</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>JOSE ALEXANDER SUAREZ ARIAS</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1130601232</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>8142a81a-7209-446d-a797-9940ba3abecd</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>JOHN ALEXANDER ARIAS RIVERA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1014248040</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>02b84e40-f930-43ed-89f0-fca0777acafb</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BRAYS ALEXANDER PORRAS ARIAS</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1014274644</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3b24e06c-2602-46f2-8bbb-2a3df6325be4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DIEGO ALEXANDER ARIAS GIL</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1016594634</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>fd076980-5666-4f30-b18d-96d3eee47d42</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DIEGO ALEXANDER MORALES ARIAS</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1067598685</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>f8debc23-d7be-43e6-a455-46f461e11485</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ALEXANDER ANDRES ARIAS TORRES</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1090455368</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>b799d80b-731d-41ab-a018-c4713558b446</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>WILSON ALEXANDER ARIAS SIGUAVITA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1098620748</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>8f659e44-e9cf-436e-bc18-06271a82d15b</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OSCAR ALEXANDER CARDENAS ARIAS</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1031126013</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0f1a15d0-a16f-4584-b41e-78f54d2b5b96</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>JIMMY ALEXANDER DIAZ ARIAS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>79915385</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>61a526ed-617a-43e1-b7a4-b17a2becd955</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>JOHN ALEXANDER ARIAS PINEDA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1035439088</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>98ca7813-4caf-486f-ab35-3c90517cd9c4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>JOHN ALEXANDER ARIAS DIAZ</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1016594705</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>c9bc9395-1df0-4fc2-8e42-077f6a379ec6</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ANDREW ALEXANDER ALBARRACIN ARIAS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1016086014</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>692c5b63-c03f-494a-98e9-8ada3cd3c7f4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>JONATHAN ALEXANDER ARIAS GUERRERO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>80214059</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>6711394f-b070-41e3-95b0-12066c186ae5</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>JOHN ALEXANDER ARIAS ARIZA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1070591755</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>8948dce0-76fd-4b0f-9215-eb6e451e4948</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>JULIAN ALEXANDER ARIAS CRUZ</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1099682581</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>8dc6bf9d-aa7d-4192-902c-2e4b3a0abe2b</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>JONATHAN ALEXANDER ARIAS OSORIO</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1118203838</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>29481033-6810-444a-aaa6-608af74973d4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DIEGO ALEXANDER ARIAS DIAZ</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1033692874</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>6b649851-20f2-4dac-9d38-949f24548e5f</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>JOHN ALEXANDER ARIAS PENA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>15372052</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>b829153e-babb-4d62-82c5-d0a2da0f51e9</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>WILMER ALEXANDER ISAZA ARIAS</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>80000350</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>38c6c422-5945-4100-9f52-e41f12723485</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>JOSE ALEXANDER MORENO ARIAS</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1192918386</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>6b23d9ce-ef71-4970-b2fb-9b3bac176e8f</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>JOHN ALEXANDER ARIAS BALLESTEROS</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>98532041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>30743569-dbcb-42cc-8f37-76fded57beeb</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DIDIER ALEXANDER MUNOZ ARIAS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1026250896</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>00ea8155-e45e-4114-8319-e8841749166d</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>JOHN ALEXANDER HENAO ARIAS</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>91507857</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1de4a18f-f1a3-4f49-9580-50dd26fb06ca</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ROBERT ALEXANDER ARIAS CAMPOS</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>14676776</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>e3ff10d3-563b-49b6-8098-51f9058ada1f</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>JHON ALEXANDER ARIAS MOISES</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1015407115</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>e77362fa-011b-4040-ac23-7333165f63e0</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>JOHN ALEXANDER CARVAJAL ARIAS</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>79712695</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>66fc1bd9-31b8-4e84-945a-8d3d5f5be037</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>JOHN ALEXANDER CASTELLANOS ARIAS</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1047485307</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5eca91c1-b6f1-4881-b40b-a66dbf277aa4</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CAMILO ALEXANDER BUSTAMANTE ARIAS</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1000637442</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>b8edc0e3-a6b1-45b7-8d72-57983f73bb0d</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>JULIAN ALEXANDER PALACIO ARIAS</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>73139406</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>12a2c29a-bbc5-484a-92c3-6e68edcea7d7</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ALEXANDER LUIS ARIAS MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1007372130</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>3498706b-2fbd-41ef-9ac6-2fda5f3d00f6</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>GUIVER ALEXANDER PERDOMO ARIAS</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1014193547</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>dd272731-d0a4-4480-bbdf-6649a41156fa</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>BRYAN ALEXANDER DIAZ ARIAS</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1017243716</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>44bf6a06-f452-4a8a-87ac-d87edba4a8e8</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>JHON ALEXANDER ARIAS MONTOYA</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1014204573</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>c9881be1-d4f6-4238-9595-b4ced3e0dfc6</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>WILLIAM ALEXANDER ARDILA ARIAS</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>10033755</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>dd21430a-d7c6-4d51-9d59-55556e610cb8</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>JOHN ALEXANDER ARIAS BATERO</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>71797854</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>cf9e030e-cd93-4b1b-8f58-36a71677fc01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>JAHIR ALEXANDER ARCILA ARIAS</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>94071295</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>9badf9b0-ae9a-43e4-ae30-f6091cdd0e9c</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MARIO ALEXANDER VALLE ARIAS</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1006415544</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>a16775e1-f81f-4c64-9e44-50de5a44efc1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>FREDY ALEXANDER SATOVA ARIAS</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>7728474</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>28e1d8cd-7a02-4c2f-b7f6-d011c731f513</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>JOSE ALEXANDER MUNOZ ARIAS</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1015468419</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>40d3f7a5-f60e-41ff-bd8b-97bf37df9bd7</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>JOHN ALEXANDER ARIAS RUBIO</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1000854654</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>e0680c6a-a187-44d7-b788-9a3928e5c667</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>MATEO ALEXANDER ARIAS VALENCIA</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1019084003</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>4b4bf163-49f2-4510-b1bc-2582bf32f409</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>JOHN ALEXANDER ARIAS TORRES</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>79816178</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0bd57df3-dccb-4d96-bc73-679b5d7ca2ec</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>FRANCK ALEXANDER RODRIGUEZ ARIAS</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1049602084</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>3cb56bb4-140c-41d1-ba0d-caa03772a6b9</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>JULIAN ALEXANDER ARIAS SAMBRANO</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1000224139</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>922608ed-aff3-406e-97ef-68768874ef8d</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>🟡 ALERTA BAJA (2 Palabras)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DANIEL ALEXANDER ARIAS URIBE</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARIAS</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/judicializadas-14-personas-que-se-dedicarian-al-trafico-local-de-estupefacientes-en-guaviare/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,53 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>URL_NOTICIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>19367079</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0f78b9c8-d783-453b-8797-0ecaa8db355c</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LUIS EDUARDO ORTIZ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>LUIS EDUARDO ORTIZ ORTIZ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-responsable-del-transporte-de-estupefacientes-en-el-tarra-norte-de-santander/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,12 +478,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19367079</t>
+          <t>79909849</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0f78b9c8-d783-453b-8797-0ecaa8db355c</t>
+          <t>d71cfb52-6370-4cba-84fc-ac3b40792fb4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -493,32 +493,361 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LUIS EDUARDO ORTIZ</t>
+          <t>OSCAR MAURICIO BALLESTEROS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LUIS EDUARDO ORTIZ ORTIZ</t>
+          <t>OSCAR MAURICIO BALLESTEROS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/afectado-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-y-homicidios-selectivos-en-armenia-y-otros-municipios-de-quindio/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1017271589</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>56ad5d1f-6ae3-40e9-9cb4-49f9711c6472</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SANTIAGO  RODRIGUEZ GIRALDO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SANTIAGO RODRIGUEZ GIRALDO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/en-valle-del-cauca-aseguran-a-11-personas-por-presunto-trafico-local-de-estupefacientes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1143990595</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0a6171ac-02b7-45e7-80bd-f9ce803d44da</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CARLOS DAVID BEJARANO MORENO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CARLOS DAVID MORENO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>75.0%</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>ESTUPEFACIENTES</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-responsable-del-transporte-de-estupefacientes-en-el-tarra-norte-de-santander/</t>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/en-valle-del-cauca-aseguran-a-11-personas-por-presunto-trafico-local-de-estupefacientes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1069750984</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>d644d399-97a1-4bac-a145-f57ed290b7ba</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CARLOS DAVID MORENO PEREZ</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CARLOS DAVID MORENO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/en-valle-del-cauca-aseguran-a-11-personas-por-presunto-trafico-local-de-estupefacientes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1023374589</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>9052db7a-c435-4399-8ee1-7c2780c298e8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CARLOS DAVID MORENO JIMENEZ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CARLOS DAVID MORENO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/en-valle-del-cauca-aseguran-a-11-personas-por-presunto-trafico-local-de-estupefacientes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1014264560</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>d6e7b77e-a41b-4253-b634-d4835dec6c30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CARLOS DAVID CUBILLOS MORENO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CARLOS DAVID MORENO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/en-valle-del-cauca-aseguran-a-11-personas-por-presunto-trafico-local-de-estupefacientes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1000855601</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>a9eb44ad-c5bc-439c-a686-f347d2f2bc5c</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CARLOS DAVID MORENO CANDIA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CARLOS DAVID MORENO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/en-valle-del-cauca-aseguran-a-11-personas-por-presunto-trafico-local-de-estupefacientes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1007005692</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>536c7a3c-03a0-4cbb-9918-2468db020674</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CARLOS DAVID MORENO ULLOA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CARLOS DAVID MORENO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ESTUPEFACIENTES</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/en-valle-del-cauca-aseguran-a-11-personas-por-presunto-trafico-local-de-estupefacientes/</t>
         </is>
       </c>
     </row>

--- a/Alerta_Fiscalia.xlsx
+++ b/Alerta_Fiscalia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,382 +472,6 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>URL_NOTICIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>79909849</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>d71cfb52-6370-4cba-84fc-ac3b40792fb4</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>OSCAR MAURICIO BALLESTEROS</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>OSCAR MAURICIO BALLESTEROS</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES, CONCIERTO PARA DELINQUIR</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/afectado-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-y-homicidios-selectivos-en-armenia-y-otros-municipios-de-quindio/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1017271589</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>56ad5d1f-6ae3-40e9-9cb4-49f9711c6472</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SANTIAGO  RODRIGUEZ GIRALDO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SANTIAGO RODRIGUEZ GIRALDO</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/en-valle-del-cauca-aseguran-a-11-personas-por-presunto-trafico-local-de-estupefacientes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1143990595</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0a6171ac-02b7-45e7-80bd-f9ce803d44da</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CARLOS DAVID BEJARANO MORENO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CARLOS DAVID MORENO</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/en-valle-del-cauca-aseguran-a-11-personas-por-presunto-trafico-local-de-estupefacientes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1069750984</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>d644d399-97a1-4bac-a145-f57ed290b7ba</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CARLOS DAVID MORENO PEREZ</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CARLOS DAVID MORENO</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/en-valle-del-cauca-aseguran-a-11-personas-por-presunto-trafico-local-de-estupefacientes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1023374589</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>9052db7a-c435-4399-8ee1-7c2780c298e8</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CARLOS DAVID MORENO JIMENEZ</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CARLOS DAVID MORENO</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/en-valle-del-cauca-aseguran-a-11-personas-por-presunto-trafico-local-de-estupefacientes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1014264560</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>d6e7b77e-a41b-4253-b634-d4835dec6c30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CARLOS DAVID CUBILLOS MORENO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CARLOS DAVID MORENO</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/en-valle-del-cauca-aseguran-a-11-personas-por-presunto-trafico-local-de-estupefacientes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1000855601</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>a9eb44ad-c5bc-439c-a686-f347d2f2bc5c</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CARLOS DAVID MORENO CANDIA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CARLOS DAVID MORENO</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/en-valle-del-cauca-aseguran-a-11-personas-por-presunto-trafico-local-de-estupefacientes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1007005692</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>536c7a3c-03a0-4cbb-9918-2468db020674</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>🟠 ALERTA MEDIA (3 Palabras)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CARLOS DAVID MORENO ULLOA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CARLOS DAVID MORENO</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ESTUPEFACIENTES</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/en-valle-del-cauca-aseguran-a-11-personas-por-presunto-trafico-local-de-estupefacientes/</t>
         </is>
       </c>
     </row>
